--- a/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_Network.xlsx
+++ b/data/Fertig - 1.a_MS_misch_base/1.a_MS_misch_grid-reduced/Power_Network.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantschnig\Desktop\Lego Pyomo\LEGO-Pyomo\data\1.a_MS_misch_grid-reduced\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Tom\Tu Graz\Masterarbeit\Git\LEGO-Pyomo\data\Fertig - 1.a_MS_misch_base\1.a_MS_misch_grid-reduced\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0AA27CF-F8A9-4756-A0D0-1EA6A002C160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6520FE9E-6A05-4078-98D5-52609D4A9C67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ScenarioA" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>None</author>
+    <author>Tom Rosenfelder</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -109,12 +110,37 @@
         </r>
       </text>
     </comment>
+    <comment ref="K10" authorId="1" shapeId="0" xr:uid="{86756C50-5578-44D7-B326-3144B6F14F4F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Tom Rosenfelder:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+100 MW groß genug damit diese virtuelle Verbindung nicht physische einschränkungen hat, aber klein genug damit das Modell noch gelöst werden kann.
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1243" uniqueCount="272">
   <si>
     <t>Power - Network</t>
   </si>
@@ -359,18 +385,9 @@
     <t>Netz-NÖ</t>
   </si>
   <si>
-    <t>kn001</t>
-  </si>
-  <si>
     <t>kn231</t>
   </si>
   <si>
-    <t>kn005</t>
-  </si>
-  <si>
-    <t>kn006</t>
-  </si>
-  <si>
     <t>kn233</t>
   </si>
   <si>
@@ -827,9 +844,6 @@
     <t>kn228</t>
   </si>
   <si>
-    <t>kn002</t>
-  </si>
-  <si>
     <t>kn232</t>
   </si>
   <si>
@@ -903,6 +917,45 @@
   </si>
   <si>
     <t>kn195</t>
+  </si>
+  <si>
+    <t>kn001_IN</t>
+  </si>
+  <si>
+    <t>kn001_PR</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>kn001_CO</t>
+  </si>
+  <si>
+    <t>kn002_IN</t>
+  </si>
+  <si>
+    <t>kn002_PR</t>
+  </si>
+  <si>
+    <t>kn002_CO</t>
+  </si>
+  <si>
+    <t>kn005_IN</t>
+  </si>
+  <si>
+    <t>kn005_PR</t>
+  </si>
+  <si>
+    <t>kn005_CO</t>
+  </si>
+  <si>
+    <t>kn006_IN</t>
+  </si>
+  <si>
+    <t>kn006_PR</t>
+  </si>
+  <si>
+    <t>kn006_CO</t>
   </si>
 </sst>
 </file>
@@ -913,7 +966,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -946,8 +999,21 @@
       <sz val="11"/>
       <name val="Aptos"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Segoe UI"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -990,6 +1056,30 @@
         <bgColor rgb="FFCCFFCC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFB8CCE4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFCCFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1003,7 +1093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1046,6 +1136,31 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1351,21 +1466,21 @@
   <sheetPr>
     <tabColor rgb="FF008080"/>
   </sheetPr>
-  <dimension ref="A1:S193"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.9375" defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:S201"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.5859375" customWidth="1"/>
-    <col min="2" max="2" width="19.703125" customWidth="1"/>
-    <col min="3" max="11" width="15.703125" customWidth="1"/>
-    <col min="12" max="12" width="19.703125" customWidth="1"/>
-    <col min="13" max="13" width="15.703125" customWidth="1"/>
-    <col min="14" max="14" width="17.703125" customWidth="1"/>
-    <col min="15" max="15" width="26.703125" customWidth="1"/>
-    <col min="16" max="17" width="20.1171875" customWidth="1"/>
-    <col min="18" max="19" width="24.5859375" customWidth="1"/>
+    <col min="1" max="1" width="5.5546875" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="11" width="15.6640625" customWidth="1"/>
+    <col min="12" max="12" width="19.6640625" customWidth="1"/>
+    <col min="13" max="13" width="15.6640625" customWidth="1"/>
+    <col min="14" max="14" width="17.6640625" customWidth="1"/>
+    <col min="15" max="15" width="26.6640625" customWidth="1"/>
+    <col min="16" max="17" width="20.109375" customWidth="1"/>
+    <col min="18" max="19" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.85">
+    <row r="1" spans="1:19" ht="24" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -1388,7 +1503,7 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
@@ -1396,7 +1511,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -1455,7 +1570,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>22</v>
       </c>
@@ -1514,7 +1629,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:19" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
       <c r="B5" s="7" t="s">
         <v>41</v>
@@ -1571,7 +1686,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="8" t="s">
         <v>59</v>
@@ -1628,7 +1743,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A7" s="9"/>
       <c r="B7" s="9" t="s">
         <v>62</v>
@@ -1685,7 +1800,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A8" s="10"/>
       <c r="B8" s="11"/>
       <c r="C8" s="12" t="s">
@@ -1728,7 +1843,7 @@
       <c r="R8" s="17"/>
       <c r="S8" s="17"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="10"/>
       <c r="B9" s="11"/>
       <c r="C9" s="12" t="s">
@@ -1775,404 +1890,370 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F10" s="13">
-        <v>4.8857999999999999E-2</v>
-      </c>
-      <c r="G10" s="13">
-        <v>2.8249E-2</v>
-      </c>
-      <c r="H10" s="13">
-        <v>5.75E-6</v>
-      </c>
-      <c r="I10" s="13">
-        <v>0</v>
-      </c>
-      <c r="J10" s="13">
-        <v>1</v>
-      </c>
-      <c r="K10" s="14">
-        <v>11.63938142686286</v>
-      </c>
-      <c r="L10" s="15">
-        <v>0</v>
-      </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="16"/>
-      <c r="O10" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="15"/>
-      <c r="R10" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S10" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A11" s="10"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="13">
-        <v>1.7406000000000001E-2</v>
-      </c>
-      <c r="G11" s="13">
-        <v>1.0064E-2</v>
-      </c>
-      <c r="H11" s="13">
-        <v>2.0499999999999999E-6</v>
-      </c>
-      <c r="I11" s="13">
-        <v>0</v>
-      </c>
-      <c r="J11" s="13">
-        <v>1</v>
-      </c>
-      <c r="K11" s="14">
-        <v>11.63938142686286</v>
-      </c>
-      <c r="L11" s="15">
-        <v>0</v>
-      </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
-      <c r="O11" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S11" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F12" s="13">
-        <v>1.7323999999999999E-2</v>
-      </c>
-      <c r="G12" s="13">
-        <v>1.0016000000000001E-2</v>
-      </c>
-      <c r="H12" s="13">
-        <v>2.04E-6</v>
-      </c>
-      <c r="I12" s="13">
-        <v>0</v>
-      </c>
-      <c r="J12" s="13">
-        <v>1</v>
-      </c>
-      <c r="K12" s="14">
-        <v>11.63938142686286</v>
-      </c>
-      <c r="L12" s="15">
-        <v>0</v>
-      </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S12" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A13" s="10"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E13" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F13" s="13">
-        <v>1.1294E-2</v>
-      </c>
-      <c r="G13" s="13">
-        <v>6.5300000000000002E-3</v>
-      </c>
-      <c r="H13" s="13">
-        <v>1.33E-6</v>
-      </c>
-      <c r="I13" s="13">
-        <v>0</v>
-      </c>
-      <c r="J13" s="13">
-        <v>1</v>
-      </c>
-      <c r="K13" s="14">
-        <v>11.63938142686286</v>
-      </c>
-      <c r="L13" s="15">
-        <v>0</v>
-      </c>
-      <c r="M13" s="16"/>
-      <c r="N13" s="16"/>
-      <c r="O13" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S13" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="13">
-        <v>1.6074999999999999E-2</v>
-      </c>
-      <c r="G14" s="13">
-        <v>9.2940000000000002E-3</v>
-      </c>
-      <c r="H14" s="13">
-        <v>1.8899999999999999E-6</v>
-      </c>
-      <c r="I14" s="13">
-        <v>0</v>
-      </c>
-      <c r="J14" s="13">
-        <v>1</v>
-      </c>
-      <c r="K14" s="14">
-        <v>11.63938142686286</v>
-      </c>
-      <c r="L14" s="15">
-        <v>0</v>
-      </c>
-      <c r="M14" s="16"/>
-      <c r="N14" s="16"/>
-      <c r="O14" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S14" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A15" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="11"/>
-      <c r="C15" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F15" s="13">
-        <v>1.4730999999999999E-2</v>
-      </c>
-      <c r="G15" s="13">
-        <v>8.5179999999999995E-3</v>
-      </c>
-      <c r="H15" s="13">
-        <v>1.73E-6</v>
-      </c>
-      <c r="I15" s="13">
-        <v>0</v>
-      </c>
-      <c r="J15" s="13">
-        <v>1</v>
-      </c>
-      <c r="K15" s="14">
-        <v>11.63938142686286</v>
-      </c>
-      <c r="L15" s="15">
-        <v>0</v>
-      </c>
-      <c r="M15" s="16"/>
-      <c r="N15" s="16"/>
-      <c r="O15" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S15" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F16" s="13">
-        <v>4.496E-3</v>
-      </c>
-      <c r="G16" s="13">
-        <v>3.908E-3</v>
-      </c>
-      <c r="H16" s="13">
-        <v>1.0300000000000001E-6</v>
-      </c>
-      <c r="I16" s="13">
-        <v>0</v>
-      </c>
-      <c r="J16" s="13">
-        <v>1</v>
-      </c>
-      <c r="K16" s="14">
-        <v>15.240315055798551</v>
-      </c>
-      <c r="L16" s="15">
-        <v>0</v>
-      </c>
-      <c r="M16" s="16"/>
-      <c r="N16" s="16"/>
-      <c r="O16" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S16" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A17" s="10"/>
-      <c r="B17" s="11"/>
-      <c r="C17" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="F17" s="13">
-        <v>2.0039999999999999E-2</v>
-      </c>
-      <c r="G17" s="13">
-        <v>8.1279999999999998E-3</v>
-      </c>
-      <c r="H17" s="13">
-        <v>1.31E-6</v>
-      </c>
-      <c r="I17" s="13">
-        <v>0</v>
-      </c>
-      <c r="J17" s="13">
-        <v>1</v>
-      </c>
-      <c r="K17" s="14">
-        <v>9.1296398066955522</v>
-      </c>
-      <c r="L17" s="15">
-        <v>0</v>
-      </c>
-      <c r="M17" s="16"/>
-      <c r="N17" s="16"/>
-      <c r="O17" s="17" t="s">
-        <v>77</v>
-      </c>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="S17" s="17" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="20" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G10" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H10" s="20">
+        <v>0</v>
+      </c>
+      <c r="I10" s="20">
+        <v>0</v>
+      </c>
+      <c r="J10" s="21">
+        <v>1</v>
+      </c>
+      <c r="K10" s="22">
+        <v>100</v>
+      </c>
+      <c r="L10" s="23">
+        <v>0</v>
+      </c>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P10" s="23"/>
+      <c r="Q10" s="23"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+    </row>
+    <row r="11" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="20" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F11" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G11" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H11" s="20">
+        <v>0</v>
+      </c>
+      <c r="I11" s="20">
+        <v>0</v>
+      </c>
+      <c r="J11" s="21">
+        <v>1</v>
+      </c>
+      <c r="K11" s="22">
+        <v>100</v>
+      </c>
+      <c r="L11" s="23">
+        <v>0</v>
+      </c>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P11" s="23"/>
+      <c r="Q11" s="23"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+    </row>
+    <row r="12" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="20" t="s">
+        <v>263</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G12" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H12" s="20">
+        <v>0</v>
+      </c>
+      <c r="I12" s="20">
+        <v>0</v>
+      </c>
+      <c r="J12" s="21">
+        <v>1</v>
+      </c>
+      <c r="K12" s="22">
+        <v>100</v>
+      </c>
+      <c r="L12" s="23">
+        <v>0</v>
+      </c>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P12" s="23"/>
+      <c r="Q12" s="23"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+    </row>
+    <row r="13" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="20" t="s">
+        <v>264</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>265</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G13" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H13" s="20">
+        <v>0</v>
+      </c>
+      <c r="I13" s="20">
+        <v>0</v>
+      </c>
+      <c r="J13" s="21">
+        <v>1</v>
+      </c>
+      <c r="K13" s="22">
+        <v>100</v>
+      </c>
+      <c r="L13" s="23">
+        <v>0</v>
+      </c>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P13" s="23"/>
+      <c r="Q13" s="23"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+    </row>
+    <row r="14" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="20" t="s">
+        <v>266</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F14" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G14" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H14" s="20">
+        <v>0</v>
+      </c>
+      <c r="I14" s="20">
+        <v>0</v>
+      </c>
+      <c r="J14" s="21">
+        <v>1</v>
+      </c>
+      <c r="K14" s="22">
+        <v>100</v>
+      </c>
+      <c r="L14" s="23">
+        <v>0</v>
+      </c>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P14" s="23"/>
+      <c r="Q14" s="23"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+    </row>
+    <row r="15" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="20" t="s">
+        <v>267</v>
+      </c>
+      <c r="D15" s="20" t="s">
+        <v>268</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G15" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H15" s="20">
+        <v>0</v>
+      </c>
+      <c r="I15" s="20">
+        <v>0</v>
+      </c>
+      <c r="J15" s="21">
+        <v>1</v>
+      </c>
+      <c r="K15" s="22">
+        <v>100</v>
+      </c>
+      <c r="L15" s="23">
+        <v>0</v>
+      </c>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P15" s="23"/>
+      <c r="Q15" s="23"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+    </row>
+    <row r="16" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="20" t="s">
+        <v>269</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F16" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G16" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H16" s="20">
+        <v>0</v>
+      </c>
+      <c r="I16" s="20">
+        <v>0</v>
+      </c>
+      <c r="J16" s="21">
+        <v>1</v>
+      </c>
+      <c r="K16" s="22">
+        <v>100</v>
+      </c>
+      <c r="L16" s="23">
+        <v>0</v>
+      </c>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P16" s="23"/>
+      <c r="Q16" s="23"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+    </row>
+    <row r="17" spans="1:19" s="26" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="20" t="s">
+        <v>270</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>271</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="G17" s="20">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="H17" s="20">
+        <v>0</v>
+      </c>
+      <c r="I17" s="20">
+        <v>0</v>
+      </c>
+      <c r="J17" s="21">
+        <v>1</v>
+      </c>
+      <c r="K17" s="22">
+        <v>100</v>
+      </c>
+      <c r="L17" s="23">
+        <v>0</v>
+      </c>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="P17" s="23"/>
+      <c r="Q17" s="23"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
-      <c r="C18" s="12" t="s">
-        <v>95</v>
+      <c r="C18" s="20" t="s">
+        <v>259</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="E18" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F18" s="13">
-        <v>6.8450000000000004E-3</v>
+        <v>4.8857999999999999E-2</v>
       </c>
       <c r="G18" s="13">
-        <v>5.9500000000000004E-3</v>
+        <v>2.8249E-2</v>
       </c>
       <c r="H18" s="13">
-        <v>1.5600000000000001E-6</v>
+        <v>5.75E-6</v>
       </c>
       <c r="I18" s="13">
         <v>0</v>
@@ -2181,7 +2262,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L18" s="15">
         <v>0</v>
@@ -2200,26 +2281,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>97</v>
+        <v>81</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>266</v>
       </c>
       <c r="E19" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F19" s="13">
-        <v>7.574E-3</v>
+        <v>1.7406000000000001E-2</v>
       </c>
       <c r="G19" s="13">
-        <v>6.5830000000000003E-3</v>
+        <v>1.0064E-2</v>
       </c>
       <c r="H19" s="13">
-        <v>1.73E-6</v>
+        <v>2.0499999999999999E-6</v>
       </c>
       <c r="I19" s="13">
         <v>0</v>
@@ -2228,7 +2309,7 @@
         <v>1</v>
       </c>
       <c r="K19" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L19" s="15">
         <v>0</v>
@@ -2247,26 +2328,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A20" s="10"/>
       <c r="B20" s="11"/>
-      <c r="C20" s="12" t="s">
-        <v>98</v>
+      <c r="C20" s="20" t="s">
+        <v>269</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="E20" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F20" s="13">
-        <v>1.2082000000000001E-2</v>
+        <v>1.7323999999999999E-2</v>
       </c>
       <c r="G20" s="13">
-        <v>6.986E-3</v>
+        <v>1.0016000000000001E-2</v>
       </c>
       <c r="H20" s="13">
-        <v>1.42E-6</v>
+        <v>2.04E-6</v>
       </c>
       <c r="I20" s="13">
         <v>0</v>
@@ -2294,26 +2375,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A21" s="10"/>
       <c r="B21" s="11"/>
       <c r="C21" s="12" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="E21" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F21" s="13">
-        <v>5.1200000000000004E-3</v>
+        <v>1.1294E-2</v>
       </c>
       <c r="G21" s="13">
-        <v>2.96E-3</v>
+        <v>6.5300000000000002E-3</v>
       </c>
       <c r="H21" s="13">
-        <v>5.9999999999999997E-7</v>
+        <v>1.33E-6</v>
       </c>
       <c r="I21" s="13">
         <v>0</v>
@@ -2341,26 +2422,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A22" s="10"/>
       <c r="B22" s="11"/>
       <c r="C22" s="12" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>102</v>
+        <v>83</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F22" s="13">
-        <v>1.512E-2</v>
+        <v>1.6074999999999999E-2</v>
       </c>
       <c r="G22" s="13">
-        <v>1.0800000000000001E-2</v>
+        <v>9.2940000000000002E-3</v>
       </c>
       <c r="H22" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>1.8899999999999999E-6</v>
       </c>
       <c r="I22" s="13">
         <v>0</v>
@@ -2369,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="K22" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L22" s="15">
         <v>0</v>
@@ -2388,26 +2469,28 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A23" s="10"/>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="B23" s="11"/>
       <c r="C23" s="12" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E23" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F23" s="13">
-        <v>7.1770000000000002E-3</v>
+        <v>1.4730999999999999E-2</v>
       </c>
       <c r="G23" s="13">
-        <v>6.2389999999999998E-3</v>
+        <v>8.5179999999999995E-3</v>
       </c>
       <c r="H23" s="13">
-        <v>1.64E-6</v>
+        <v>1.73E-6</v>
       </c>
       <c r="I23" s="13">
         <v>0</v>
@@ -2416,7 +2499,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L23" s="15">
         <v>0</v>
@@ -2435,26 +2518,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A24" s="10"/>
       <c r="B24" s="11"/>
       <c r="C24" s="12" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="E24" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F24" s="13">
-        <v>1.3099E-2</v>
+        <v>4.496E-3</v>
       </c>
       <c r="G24" s="13">
-        <v>5.313E-3</v>
+        <v>3.908E-3</v>
       </c>
       <c r="H24" s="13">
-        <v>8.6000000000000002E-7</v>
+        <v>1.0300000000000001E-6</v>
       </c>
       <c r="I24" s="13">
         <v>0</v>
@@ -2463,7 +2546,7 @@
         <v>1</v>
       </c>
       <c r="K24" s="14">
-        <v>9.1296398066955522</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L24" s="15">
         <v>0</v>
@@ -2482,26 +2565,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A25" s="10"/>
       <c r="B25" s="11"/>
       <c r="C25" s="12" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="E25" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F25" s="13">
-        <v>1.1416000000000001E-2</v>
+        <v>2.0039999999999999E-2</v>
       </c>
       <c r="G25" s="13">
-        <v>6.6E-3</v>
+        <v>8.1279999999999998E-3</v>
       </c>
       <c r="H25" s="13">
-        <v>1.3400000000000001E-6</v>
+        <v>1.31E-6</v>
       </c>
       <c r="I25" s="13">
         <v>0</v>
@@ -2510,7 +2593,7 @@
         <v>1</v>
       </c>
       <c r="K25" s="14">
-        <v>11.63938142686286</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L25" s="15">
         <v>0</v>
@@ -2529,26 +2612,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A26" s="10"/>
       <c r="B26" s="11"/>
       <c r="C26" s="12" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="E26" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F26" s="13">
-        <v>8.2389999999999998E-3</v>
+        <v>6.8450000000000004E-3</v>
       </c>
       <c r="G26" s="13">
-        <v>4.764E-3</v>
+        <v>5.9500000000000004E-3</v>
       </c>
       <c r="H26" s="13">
-        <v>9.7000000000000003E-7</v>
+        <v>1.5600000000000001E-6</v>
       </c>
       <c r="I26" s="13">
         <v>0</v>
@@ -2557,7 +2640,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L26" s="15">
         <v>0</v>
@@ -2576,26 +2659,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A27" s="10"/>
       <c r="B27" s="11"/>
       <c r="C27" s="12" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="E27" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F27" s="13">
-        <v>6.3E-3</v>
+        <v>7.574E-3</v>
       </c>
       <c r="G27" s="13">
-        <v>5.476E-3</v>
+        <v>6.5830000000000003E-3</v>
       </c>
       <c r="H27" s="13">
-        <v>1.44E-6</v>
+        <v>1.73E-6</v>
       </c>
       <c r="I27" s="13">
         <v>0</v>
@@ -2623,26 +2706,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A28" s="10"/>
       <c r="B28" s="11"/>
       <c r="C28" s="12" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="E28" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F28" s="13">
-        <v>5.1019999999999998E-3</v>
+        <v>1.2082000000000001E-2</v>
       </c>
       <c r="G28" s="13">
-        <v>4.4349999999999997E-3</v>
+        <v>6.986E-3</v>
       </c>
       <c r="H28" s="13">
-        <v>1.17E-6</v>
+        <v>1.42E-6</v>
       </c>
       <c r="I28" s="13">
         <v>0</v>
@@ -2651,7 +2734,7 @@
         <v>1</v>
       </c>
       <c r="K28" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L28" s="15">
         <v>0</v>
@@ -2670,26 +2753,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A29" s="10"/>
       <c r="B29" s="11"/>
       <c r="C29" s="12" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="E29" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F29" s="13">
-        <v>9.5790000000000007E-3</v>
+        <v>5.1200000000000004E-3</v>
       </c>
       <c r="G29" s="13">
-        <v>5.5389999999999997E-3</v>
+        <v>2.96E-3</v>
       </c>
       <c r="H29" s="13">
-        <v>1.13E-6</v>
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="I29" s="13">
         <v>0</v>
@@ -2717,26 +2800,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="11"/>
       <c r="C30" s="12" t="s">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="E30" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F30" s="13">
-        <v>1.4534999999999999E-2</v>
+        <v>1.512E-2</v>
       </c>
       <c r="G30" s="13">
-        <v>5.8950000000000001E-3</v>
+        <v>1.0800000000000001E-2</v>
       </c>
       <c r="H30" s="13">
-        <v>9.5000000000000001E-7</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I30" s="13">
         <v>0</v>
@@ -2745,7 +2828,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="14">
-        <v>9.1296398066955522</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L30" s="15">
         <v>0</v>
@@ -2764,26 +2847,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A31" s="10"/>
       <c r="B31" s="11"/>
       <c r="C31" s="12" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F31" s="13">
-        <v>7.1970000000000003E-3</v>
+        <v>7.1770000000000002E-3</v>
       </c>
       <c r="G31" s="13">
-        <v>4.1619999999999999E-3</v>
+        <v>6.2389999999999998E-3</v>
       </c>
       <c r="H31" s="13">
-        <v>8.5000000000000001E-7</v>
+        <v>1.64E-6</v>
       </c>
       <c r="I31" s="13">
         <v>0</v>
@@ -2792,7 +2875,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L31" s="15">
         <v>0</v>
@@ -2811,26 +2894,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A32" s="10"/>
       <c r="B32" s="11"/>
       <c r="C32" s="12" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>117</v>
+        <v>102</v>
       </c>
       <c r="E32" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F32" s="13">
-        <v>9.0010000000000003E-3</v>
+        <v>1.3099E-2</v>
       </c>
       <c r="G32" s="13">
-        <v>5.2050000000000004E-3</v>
+        <v>5.313E-3</v>
       </c>
       <c r="H32" s="13">
-        <v>1.06E-6</v>
+        <v>8.6000000000000002E-7</v>
       </c>
       <c r="I32" s="13">
         <v>0</v>
@@ -2839,7 +2922,7 @@
         <v>1</v>
       </c>
       <c r="K32" s="14">
-        <v>11.63938142686286</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L32" s="15">
         <v>0</v>
@@ -2858,26 +2941,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A33" s="10"/>
       <c r="B33" s="11"/>
       <c r="C33" s="12" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F33" s="13">
-        <v>7.9360000000000003E-3</v>
+        <v>1.1416000000000001E-2</v>
       </c>
       <c r="G33" s="13">
-        <v>4.5880000000000001E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="H33" s="13">
-        <v>9.2999999999999999E-7</v>
+        <v>1.3400000000000001E-6</v>
       </c>
       <c r="I33" s="13">
         <v>0</v>
@@ -2905,28 +2988,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A34" s="10" t="s">
-        <v>9</v>
-      </c>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="10"/>
       <c r="B34" s="11"/>
       <c r="C34" s="12" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="E34" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F34" s="13">
-        <v>5.2760000000000003E-3</v>
+        <v>8.2389999999999998E-3</v>
       </c>
       <c r="G34" s="13">
-        <v>3.0500000000000002E-3</v>
+        <v>4.764E-3</v>
       </c>
       <c r="H34" s="13">
-        <v>6.1999999999999999E-7</v>
+        <v>9.7000000000000003E-7</v>
       </c>
       <c r="I34" s="13">
         <v>0</v>
@@ -2954,26 +3035,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A35" s="10"/>
       <c r="B35" s="11"/>
       <c r="C35" s="12" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="E35" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F35" s="13">
-        <v>1.2400000000000001E-4</v>
+        <v>6.3E-3</v>
       </c>
       <c r="G35" s="13">
-        <v>1.08E-4</v>
+        <v>5.476E-3</v>
       </c>
       <c r="H35" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>1.44E-6</v>
       </c>
       <c r="I35" s="13">
         <v>0</v>
@@ -3001,26 +3082,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A36" s="10"/>
       <c r="B36" s="11"/>
       <c r="C36" s="12" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="D36" s="12" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="E36" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F36" s="13">
-        <v>1.2033E-2</v>
+        <v>5.1019999999999998E-3</v>
       </c>
       <c r="G36" s="13">
-        <v>4.8799999999999998E-3</v>
+        <v>4.4349999999999997E-3</v>
       </c>
       <c r="H36" s="13">
-        <v>7.8999999999999995E-7</v>
+        <v>1.17E-6</v>
       </c>
       <c r="I36" s="13">
         <v>0</v>
@@ -3029,7 +3110,7 @@
         <v>1</v>
       </c>
       <c r="K36" s="14">
-        <v>9.1296398066955522</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L36" s="15">
         <v>0</v>
@@ -3048,26 +3129,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A37" s="10"/>
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="s">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="E37" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F37" s="13">
-        <v>4.7429999999999998E-3</v>
+        <v>9.5790000000000007E-3</v>
       </c>
       <c r="G37" s="13">
-        <v>4.1219999999999998E-3</v>
+        <v>5.5389999999999997E-3</v>
       </c>
       <c r="H37" s="13">
-        <v>1.08E-6</v>
+        <v>1.13E-6</v>
       </c>
       <c r="I37" s="13">
         <v>0</v>
@@ -3076,7 +3157,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L37" s="15">
         <v>0</v>
@@ -3095,26 +3176,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A38" s="10"/>
       <c r="B38" s="11"/>
       <c r="C38" s="12" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="E38" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F38" s="13">
-        <v>4.3639999999999998E-3</v>
+        <v>1.4534999999999999E-2</v>
       </c>
       <c r="G38" s="13">
-        <v>3.7929999999999999E-3</v>
+        <v>5.8950000000000001E-3</v>
       </c>
       <c r="H38" s="13">
-        <v>9.9999999999999995E-7</v>
+        <v>9.5000000000000001E-7</v>
       </c>
       <c r="I38" s="13">
         <v>0</v>
@@ -3123,7 +3204,7 @@
         <v>1</v>
       </c>
       <c r="K38" s="14">
-        <v>15.240315055798551</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L38" s="15">
         <v>0</v>
@@ -3142,26 +3223,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A39" s="10"/>
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="E39" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F39" s="13">
-        <v>4.6280000000000002E-3</v>
+        <v>7.1970000000000003E-3</v>
       </c>
       <c r="G39" s="13">
-        <v>4.0220000000000004E-3</v>
+        <v>4.1619999999999999E-3</v>
       </c>
       <c r="H39" s="13">
-        <v>1.06E-6</v>
+        <v>8.5000000000000001E-7</v>
       </c>
       <c r="I39" s="13">
         <v>0</v>
@@ -3170,7 +3251,7 @@
         <v>1</v>
       </c>
       <c r="K39" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L39" s="15">
         <v>0</v>
@@ -3189,26 +3270,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A40" s="10"/>
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="E40" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F40" s="13">
-        <v>7.2150000000000001E-3</v>
+        <v>9.0010000000000003E-3</v>
       </c>
       <c r="G40" s="13">
-        <v>4.1720000000000004E-3</v>
+        <v>5.2050000000000004E-3</v>
       </c>
       <c r="H40" s="13">
-        <v>8.5000000000000001E-7</v>
+        <v>1.06E-6</v>
       </c>
       <c r="I40" s="13">
         <v>0</v>
@@ -3236,26 +3317,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A41" s="10"/>
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E41" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F41" s="13">
-        <v>1.35E-4</v>
+        <v>7.9360000000000003E-3</v>
       </c>
       <c r="G41" s="13">
-        <v>1.17E-4</v>
+        <v>4.5880000000000001E-3</v>
       </c>
       <c r="H41" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>9.2999999999999999E-7</v>
       </c>
       <c r="I41" s="13">
         <v>0</v>
@@ -3264,7 +3345,7 @@
         <v>1</v>
       </c>
       <c r="K41" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L41" s="15">
         <v>0</v>
@@ -3283,26 +3364,28 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.5">
-      <c r="A42" s="10"/>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" s="10" t="s">
+        <v>9</v>
+      </c>
       <c r="B42" s="11"/>
       <c r="C42" s="12" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="E42" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F42" s="13">
-        <v>7.1269999999999997E-3</v>
+        <v>5.2760000000000003E-3</v>
       </c>
       <c r="G42" s="13">
-        <v>4.1209999999999997E-3</v>
+        <v>3.0500000000000002E-3</v>
       </c>
       <c r="H42" s="13">
-        <v>8.4E-7</v>
+        <v>6.1999999999999999E-7</v>
       </c>
       <c r="I42" s="13">
         <v>0</v>
@@ -3330,26 +3413,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A43" s="10"/>
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="E43" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F43" s="13">
-        <v>3.6200000000000002E-4</v>
+        <v>1.2400000000000001E-4</v>
       </c>
       <c r="G43" s="13">
-        <v>2.0900000000000001E-4</v>
+        <v>1.08E-4</v>
       </c>
       <c r="H43" s="13">
-        <v>4.0000000000000001E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I43" s="13">
         <v>0</v>
@@ -3358,7 +3441,7 @@
         <v>1</v>
       </c>
       <c r="K43" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L43" s="15">
         <v>0</v>
@@ -3377,26 +3460,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A44" s="10"/>
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F44" s="13">
-        <v>4.2659999999999998E-3</v>
+        <v>1.2033E-2</v>
       </c>
       <c r="G44" s="13">
-        <v>3.7090000000000001E-3</v>
+        <v>4.8799999999999998E-3</v>
       </c>
       <c r="H44" s="13">
-        <v>9.7999999999999993E-7</v>
+        <v>7.8999999999999995E-7</v>
       </c>
       <c r="I44" s="13">
         <v>0</v>
@@ -3405,7 +3488,7 @@
         <v>1</v>
       </c>
       <c r="K44" s="14">
-        <v>15.240315055798551</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L44" s="15">
         <v>0</v>
@@ -3424,26 +3507,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A45" s="10"/>
       <c r="B45" s="11"/>
       <c r="C45" s="12" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F45" s="13">
-        <v>3.7729999999999999E-3</v>
+        <v>4.7429999999999998E-3</v>
       </c>
       <c r="G45" s="13">
-        <v>3.2789999999999998E-3</v>
+        <v>4.1219999999999998E-3</v>
       </c>
       <c r="H45" s="13">
-        <v>8.6000000000000002E-7</v>
+        <v>1.08E-6</v>
       </c>
       <c r="I45" s="13">
         <v>0</v>
@@ -3471,26 +3554,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A46" s="10"/>
       <c r="B46" s="11"/>
       <c r="C46" s="12" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F46" s="13">
-        <v>6.7429999999999999E-3</v>
+        <v>4.3639999999999998E-3</v>
       </c>
       <c r="G46" s="13">
-        <v>3.8990000000000001E-3</v>
+        <v>3.7929999999999999E-3</v>
       </c>
       <c r="H46" s="13">
-        <v>7.8999999999999995E-7</v>
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="I46" s="13">
         <v>0</v>
@@ -3499,7 +3582,7 @@
         <v>1</v>
       </c>
       <c r="K46" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L46" s="15">
         <v>0</v>
@@ -3518,26 +3601,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A47" s="10"/>
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="E47" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F47" s="13">
-        <v>6.1069999999999996E-3</v>
+        <v>4.6280000000000002E-3</v>
       </c>
       <c r="G47" s="13">
-        <v>3.5309999999999999E-3</v>
+        <v>4.0220000000000004E-3</v>
       </c>
       <c r="H47" s="13">
-        <v>7.1999999999999999E-7</v>
+        <v>1.06E-6</v>
       </c>
       <c r="I47" s="13">
         <v>0</v>
@@ -3546,7 +3629,7 @@
         <v>1</v>
       </c>
       <c r="K47" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L47" s="15">
         <v>0</v>
@@ -3565,26 +3648,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A48" s="10"/>
       <c r="B48" s="11"/>
       <c r="C48" s="12" t="s">
-        <v>140</v>
+        <v>83</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>93</v>
+        <v>129</v>
       </c>
       <c r="E48" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F48" s="13">
-        <v>6.5189999999999996E-3</v>
+        <v>7.2150000000000001E-3</v>
       </c>
       <c r="G48" s="13">
-        <v>3.7699999999999999E-3</v>
+        <v>4.1720000000000004E-3</v>
       </c>
       <c r="H48" s="13">
-        <v>7.7000000000000004E-7</v>
+        <v>8.5000000000000001E-7</v>
       </c>
       <c r="I48" s="13">
         <v>0</v>
@@ -3612,26 +3695,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A49" s="10"/>
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="E49" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F49" s="13">
-        <v>9.7599999999999996E-3</v>
+        <v>1.35E-4</v>
       </c>
       <c r="G49" s="13">
-        <v>3.9589999999999998E-3</v>
+        <v>1.17E-4</v>
       </c>
       <c r="H49" s="13">
-        <v>6.4000000000000001E-7</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I49" s="13">
         <v>0</v>
@@ -3640,7 +3723,7 @@
         <v>1</v>
       </c>
       <c r="K49" s="14">
-        <v>9.1296398066955522</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L49" s="15">
         <v>0</v>
@@ -3659,26 +3742,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A50" s="10"/>
       <c r="B50" s="11"/>
       <c r="C50" s="12" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="E50" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F50" s="13">
-        <v>6.3629999999999997E-3</v>
+        <v>7.1269999999999997E-3</v>
       </c>
       <c r="G50" s="13">
-        <v>3.679E-3</v>
+        <v>4.1209999999999997E-3</v>
       </c>
       <c r="H50" s="13">
-        <v>7.5000000000000002E-7</v>
+        <v>8.4E-7</v>
       </c>
       <c r="I50" s="13">
         <v>0</v>
@@ -3706,26 +3789,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A51" s="10"/>
       <c r="B51" s="11"/>
       <c r="C51" s="12" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="E51" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F51" s="13">
-        <v>1.702E-3</v>
+        <v>3.6200000000000002E-4</v>
       </c>
       <c r="G51" s="13">
-        <v>1.48E-3</v>
+        <v>2.0900000000000001E-4</v>
       </c>
       <c r="H51" s="13">
-        <v>3.9000000000000002E-7</v>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="I51" s="13">
         <v>0</v>
@@ -3734,7 +3817,7 @@
         <v>1</v>
       </c>
       <c r="K51" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L51" s="15">
         <v>0</v>
@@ -3753,26 +3836,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A52" s="10"/>
       <c r="B52" s="11"/>
       <c r="C52" s="12" t="s">
-        <v>144</v>
+        <v>93</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F52" s="13">
-        <v>3.771E-3</v>
+        <v>4.2659999999999998E-3</v>
       </c>
       <c r="G52" s="13">
-        <v>3.2780000000000001E-3</v>
+        <v>3.7090000000000001E-3</v>
       </c>
       <c r="H52" s="13">
-        <v>8.6000000000000002E-7</v>
+        <v>9.7999999999999993E-7</v>
       </c>
       <c r="I52" s="13">
         <v>0</v>
@@ -3800,26 +3883,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A53" s="10"/>
       <c r="B53" s="11"/>
       <c r="C53" s="12" t="s">
-        <v>145</v>
+        <v>266</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E53" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F53" s="13">
-        <v>3.7199999999999999E-4</v>
+        <v>3.7729999999999999E-3</v>
       </c>
       <c r="G53" s="13">
-        <v>2.1499999999999999E-4</v>
+        <v>3.2789999999999998E-3</v>
       </c>
       <c r="H53" s="13">
-        <v>4.0000000000000001E-8</v>
+        <v>8.6000000000000002E-7</v>
       </c>
       <c r="I53" s="13">
         <v>0</v>
@@ -3828,7 +3911,7 @@
         <v>1</v>
       </c>
       <c r="K53" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L53" s="15">
         <v>0</v>
@@ -3847,26 +3930,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A54" s="10"/>
       <c r="B54" s="11"/>
       <c r="C54" s="12" t="s">
-        <v>101</v>
+        <v>134</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E54" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F54" s="13">
-        <v>5.9979999999999999E-3</v>
+        <v>6.7429999999999999E-3</v>
       </c>
       <c r="G54" s="13">
-        <v>3.4680000000000002E-3</v>
+        <v>3.8990000000000001E-3</v>
       </c>
       <c r="H54" s="13">
-        <v>7.0999999999999998E-7</v>
+        <v>7.8999999999999995E-7</v>
       </c>
       <c r="I54" s="13">
         <v>0</v>
@@ -3894,26 +3977,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A55" s="10"/>
       <c r="B55" s="11"/>
       <c r="C55" s="12" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F55" s="13">
-        <v>5.8329999999999996E-3</v>
+        <v>6.1069999999999996E-3</v>
       </c>
       <c r="G55" s="13">
-        <v>3.3730000000000001E-3</v>
+        <v>3.5309999999999999E-3</v>
       </c>
       <c r="H55" s="13">
-        <v>6.8999999999999996E-7</v>
+        <v>7.1999999999999999E-7</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
@@ -3941,26 +4024,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A56" s="10"/>
       <c r="B56" s="11"/>
       <c r="C56" s="12" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F56" s="13">
-        <v>4.7699999999999999E-4</v>
+        <v>6.5189999999999996E-3</v>
       </c>
       <c r="G56" s="13">
-        <v>2.7599999999999999E-4</v>
+        <v>3.7699999999999999E-3</v>
       </c>
       <c r="H56" s="13">
-        <v>5.9999999999999995E-8</v>
+        <v>7.7000000000000004E-7</v>
       </c>
       <c r="I56" s="13">
         <v>0</v>
@@ -3988,26 +4071,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A57" s="10"/>
       <c r="B57" s="11"/>
       <c r="C57" s="12" t="s">
-        <v>149</v>
+        <v>123</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="E57" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F57" s="13">
-        <v>5.9890000000000004E-3</v>
+        <v>9.7599999999999996E-3</v>
       </c>
       <c r="G57" s="13">
-        <v>3.4629999999999999E-3</v>
+        <v>3.9589999999999998E-3</v>
       </c>
       <c r="H57" s="13">
-        <v>6.9999999999999997E-7</v>
+        <v>6.4000000000000001E-7</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -4016,7 +4099,7 @@
         <v>1</v>
       </c>
       <c r="K57" s="14">
-        <v>11.63938142686286</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L57" s="15">
         <v>0</v>
@@ -4035,26 +4118,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A58" s="10"/>
       <c r="B58" s="11"/>
       <c r="C58" s="12" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E58" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F58" s="13">
-        <v>5.7270000000000003E-3</v>
+        <v>6.3629999999999997E-3</v>
       </c>
       <c r="G58" s="13">
-        <v>3.3110000000000001E-3</v>
+        <v>3.679E-3</v>
       </c>
       <c r="H58" s="13">
-        <v>6.7000000000000004E-7</v>
+        <v>7.5000000000000002E-7</v>
       </c>
       <c r="I58" s="13">
         <v>0</v>
@@ -4082,26 +4165,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A59" s="10"/>
       <c r="B59" s="11"/>
       <c r="C59" s="12" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>152</v>
+        <v>119</v>
       </c>
       <c r="E59" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F59" s="13">
-        <v>5.5750000000000001E-3</v>
+        <v>1.702E-3</v>
       </c>
       <c r="G59" s="13">
-        <v>3.2239999999999999E-3</v>
+        <v>1.48E-3</v>
       </c>
       <c r="H59" s="13">
-        <v>6.6000000000000003E-7</v>
+        <v>3.9000000000000002E-7</v>
       </c>
       <c r="I59" s="13">
         <v>0</v>
@@ -4110,7 +4193,7 @@
         <v>1</v>
       </c>
       <c r="K59" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L59" s="15">
         <v>0</v>
@@ -4129,26 +4212,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A60" s="10"/>
       <c r="B60" s="11"/>
       <c r="C60" s="12" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="E60" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F60" s="13">
-        <v>3.4329999999999999E-3</v>
+        <v>3.771E-3</v>
       </c>
       <c r="G60" s="13">
-        <v>2.9840000000000001E-3</v>
+        <v>3.2780000000000001E-3</v>
       </c>
       <c r="H60" s="13">
-        <v>7.8000000000000005E-7</v>
+        <v>8.6000000000000002E-7</v>
       </c>
       <c r="I60" s="13">
         <v>0</v>
@@ -4176,26 +4259,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A61" s="10"/>
       <c r="B61" s="11"/>
       <c r="C61" s="12" t="s">
-        <v>102</v>
+        <v>142</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
       <c r="E61" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F61" s="13">
-        <v>5.3169999999999997E-3</v>
+        <v>3.7199999999999999E-4</v>
       </c>
       <c r="G61" s="13">
-        <v>3.075E-3</v>
+        <v>2.1499999999999999E-4</v>
       </c>
       <c r="H61" s="13">
-        <v>6.3E-7</v>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="I61" s="13">
         <v>0</v>
@@ -4223,26 +4306,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A62" s="10"/>
       <c r="B62" s="11"/>
       <c r="C62" s="12" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="E62" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F62" s="13">
-        <v>3.264E-3</v>
+        <v>5.9979999999999999E-3</v>
       </c>
       <c r="G62" s="13">
-        <v>2.8370000000000001E-3</v>
+        <v>3.4680000000000002E-3</v>
       </c>
       <c r="H62" s="13">
-        <v>7.5000000000000002E-7</v>
+        <v>7.0999999999999998E-7</v>
       </c>
       <c r="I62" s="13">
         <v>0</v>
@@ -4251,7 +4334,7 @@
         <v>1</v>
       </c>
       <c r="K62" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L62" s="15">
         <v>0</v>
@@ -4270,26 +4353,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A63" s="10"/>
       <c r="B63" s="11"/>
       <c r="C63" s="12" t="s">
-        <v>121</v>
+        <v>143</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="E63" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F63" s="13">
-        <v>5.2059999999999997E-3</v>
+        <v>5.8329999999999996E-3</v>
       </c>
       <c r="G63" s="13">
-        <v>3.0100000000000001E-3</v>
+        <v>3.3730000000000001E-3</v>
       </c>
       <c r="H63" s="13">
-        <v>6.0999999999999998E-7</v>
+        <v>6.8999999999999996E-7</v>
       </c>
       <c r="I63" s="13">
         <v>0</v>
@@ -4317,26 +4400,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A64" s="10"/>
       <c r="B64" s="11"/>
       <c r="C64" s="12" t="s">
-        <v>157</v>
+        <v>110</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="E64" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F64" s="13">
-        <v>1.018E-3</v>
+        <v>4.7699999999999999E-4</v>
       </c>
       <c r="G64" s="13">
-        <v>8.8500000000000004E-4</v>
+        <v>2.7599999999999999E-4</v>
       </c>
       <c r="H64" s="13">
-        <v>2.2999999999999999E-7</v>
+        <v>5.9999999999999995E-8</v>
       </c>
       <c r="I64" s="13">
         <v>0</v>
@@ -4345,7 +4428,7 @@
         <v>1</v>
       </c>
       <c r="K64" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L64" s="15">
         <v>0</v>
@@ -4364,26 +4447,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A65" s="10"/>
       <c r="B65" s="11"/>
       <c r="C65" s="12" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="E65" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F65" s="13">
-        <v>7.9209999999999992E-3</v>
+        <v>5.9890000000000004E-3</v>
       </c>
       <c r="G65" s="13">
-        <v>3.2130000000000001E-3</v>
+        <v>3.4629999999999999E-3</v>
       </c>
       <c r="H65" s="13">
-        <v>5.2E-7</v>
+        <v>6.9999999999999997E-7</v>
       </c>
       <c r="I65" s="13">
         <v>0</v>
@@ -4392,7 +4475,7 @@
         <v>1</v>
       </c>
       <c r="K65" s="14">
-        <v>9.1296398066955522</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L65" s="15">
         <v>0</v>
@@ -4411,26 +4494,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A66" s="10"/>
       <c r="B66" s="11"/>
       <c r="C66" s="12" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="E66" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F66" s="13">
-        <v>3.29E-3</v>
+        <v>5.7270000000000003E-3</v>
       </c>
       <c r="G66" s="13">
-        <v>1.3339999999999999E-3</v>
+        <v>3.3110000000000001E-3</v>
       </c>
       <c r="H66" s="13">
-        <v>2.2000000000000001E-7</v>
+        <v>6.7000000000000004E-7</v>
       </c>
       <c r="I66" s="13">
         <v>0</v>
@@ -4439,7 +4522,7 @@
         <v>1</v>
       </c>
       <c r="K66" s="14">
-        <v>9.1296398066955522</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L66" s="15">
         <v>0</v>
@@ -4458,26 +4541,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A67" s="10"/>
       <c r="B67" s="11"/>
       <c r="C67" s="12" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="E67" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F67" s="13">
-        <v>8.0450000000000001E-3</v>
+        <v>5.5750000000000001E-3</v>
       </c>
       <c r="G67" s="13">
-        <v>3.1697999999999997E-2</v>
+        <v>3.2239999999999999E-3</v>
       </c>
       <c r="H67" s="13">
-        <v>7.0000000000000005E-8</v>
+        <v>6.6000000000000003E-7</v>
       </c>
       <c r="I67" s="13">
         <v>0</v>
@@ -4486,7 +4569,7 @@
         <v>1</v>
       </c>
       <c r="K67" s="14">
-        <v>6.5471520526103566</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L67" s="15">
         <v>0</v>
@@ -4505,26 +4588,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A68" s="10"/>
       <c r="B68" s="11"/>
       <c r="C68" s="12" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>89</v>
+        <v>151</v>
       </c>
       <c r="E68" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F68" s="13">
-        <v>2.4589999999999998E-3</v>
+        <v>3.4329999999999999E-3</v>
       </c>
       <c r="G68" s="13">
-        <v>2.1380000000000001E-3</v>
+        <v>2.9840000000000001E-3</v>
       </c>
       <c r="H68" s="13">
-        <v>5.6000000000000004E-7</v>
+        <v>7.8000000000000005E-7</v>
       </c>
       <c r="I68" s="13">
         <v>0</v>
@@ -4552,26 +4635,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A69" s="10"/>
       <c r="B69" s="11"/>
       <c r="C69" s="12" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="E69" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F69" s="13">
-        <v>3.3100000000000002E-4</v>
+        <v>5.3169999999999997E-3</v>
       </c>
       <c r="G69" s="13">
-        <v>2.8800000000000001E-4</v>
+        <v>3.075E-3</v>
       </c>
       <c r="H69" s="13">
-        <v>8.0000000000000002E-8</v>
+        <v>6.3E-7</v>
       </c>
       <c r="I69" s="13">
         <v>0</v>
@@ -4580,7 +4663,7 @@
         <v>1</v>
       </c>
       <c r="K69" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L69" s="15">
         <v>0</v>
@@ -4599,26 +4682,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A70" s="10"/>
       <c r="B70" s="11"/>
       <c r="C70" s="12" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E70" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F70" s="13">
-        <v>2.4039999999999999E-3</v>
+        <v>3.264E-3</v>
       </c>
       <c r="G70" s="13">
-        <v>2.0899999999999998E-3</v>
+        <v>2.8370000000000001E-3</v>
       </c>
       <c r="H70" s="13">
-        <v>5.5000000000000003E-7</v>
+        <v>7.5000000000000002E-7</v>
       </c>
       <c r="I70" s="13">
         <v>0</v>
@@ -4646,26 +4729,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A71" s="10"/>
       <c r="B71" s="11"/>
       <c r="C71" s="12" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="D71" s="12" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="E71" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F71" s="13">
-        <v>3.9439999999999996E-3</v>
+        <v>5.2059999999999997E-3</v>
       </c>
       <c r="G71" s="13">
-        <v>2.281E-3</v>
+        <v>3.0100000000000001E-3</v>
       </c>
       <c r="H71" s="13">
-        <v>4.5999999999999999E-7</v>
+        <v>6.0999999999999998E-7</v>
       </c>
       <c r="I71" s="13">
         <v>0</v>
@@ -4693,26 +4776,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A72" s="10"/>
       <c r="B72" s="11"/>
       <c r="C72" s="12" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="D72" s="12" t="s">
-        <v>167</v>
+        <v>85</v>
       </c>
       <c r="E72" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F72" s="13">
-        <v>5.4289999999999998E-3</v>
+        <v>1.018E-3</v>
       </c>
       <c r="G72" s="13">
-        <v>2.202E-3</v>
+        <v>8.8500000000000004E-4</v>
       </c>
       <c r="H72" s="13">
-        <v>3.4999999999999998E-7</v>
+        <v>2.2999999999999999E-7</v>
       </c>
       <c r="I72" s="13">
         <v>0</v>
@@ -4721,7 +4804,7 @@
         <v>1</v>
       </c>
       <c r="K72" s="14">
-        <v>9.1296398066955522</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L72" s="15">
         <v>0</v>
@@ -4740,26 +4823,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A73" s="10"/>
       <c r="B73" s="11"/>
       <c r="C73" s="12" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="D73" s="12" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="E73" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F73" s="13">
-        <v>6.2049999999999996E-3</v>
+        <v>7.9209999999999992E-3</v>
       </c>
       <c r="G73" s="13">
-        <v>4.4320000000000002E-3</v>
+        <v>3.2130000000000001E-3</v>
       </c>
       <c r="H73" s="13">
-        <v>1E-8</v>
+        <v>5.2E-7</v>
       </c>
       <c r="I73" s="13">
         <v>0</v>
@@ -4768,7 +4851,7 @@
         <v>1</v>
       </c>
       <c r="K73" s="14">
-        <v>9.2751320745313386</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L73" s="15">
         <v>0</v>
@@ -4787,26 +4870,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A74" s="10"/>
       <c r="B74" s="11"/>
       <c r="C74" s="12" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F74" s="13">
-        <v>2.1640000000000001E-3</v>
+        <v>3.29E-3</v>
       </c>
       <c r="G74" s="13">
-        <v>1.882E-3</v>
+        <v>1.3339999999999999E-3</v>
       </c>
       <c r="H74" s="13">
-        <v>4.8999999999999997E-7</v>
+        <v>2.2000000000000001E-7</v>
       </c>
       <c r="I74" s="13">
         <v>0</v>
@@ -4815,7 +4898,7 @@
         <v>1</v>
       </c>
       <c r="K74" s="14">
-        <v>15.240315055798551</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L74" s="15">
         <v>0</v>
@@ -4834,26 +4917,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A75" s="10"/>
       <c r="B75" s="11"/>
       <c r="C75" s="12" t="s">
-        <v>117</v>
+        <v>158</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="E75" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F75" s="13">
-        <v>5.0280000000000004E-3</v>
+        <v>8.0450000000000001E-3</v>
       </c>
       <c r="G75" s="13">
-        <v>2.039E-3</v>
+        <v>3.1697999999999997E-2</v>
       </c>
       <c r="H75" s="13">
-        <v>3.3000000000000002E-7</v>
+        <v>7.0000000000000005E-8</v>
       </c>
       <c r="I75" s="13">
         <v>0</v>
@@ -4862,7 +4945,7 @@
         <v>1</v>
       </c>
       <c r="K75" s="14">
-        <v>9.1296398066955522</v>
+        <v>6.5471520526103566</v>
       </c>
       <c r="L75" s="15">
         <v>0</v>
@@ -4881,26 +4964,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A76" s="10"/>
       <c r="B76" s="11"/>
       <c r="C76" s="12" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E76" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F76" s="13">
-        <v>2.0070000000000001E-3</v>
+        <v>2.4589999999999998E-3</v>
       </c>
       <c r="G76" s="13">
-        <v>1.745E-3</v>
+        <v>2.1380000000000001E-3</v>
       </c>
       <c r="H76" s="13">
-        <v>4.5999999999999999E-7</v>
+        <v>5.6000000000000004E-7</v>
       </c>
       <c r="I76" s="13">
         <v>0</v>
@@ -4928,26 +5011,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A77" s="10"/>
       <c r="B77" s="11"/>
       <c r="C77" s="12" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="E77" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F77" s="13">
-        <v>3.1670000000000001E-3</v>
+        <v>3.3100000000000002E-4</v>
       </c>
       <c r="G77" s="13">
-        <v>1.8309999999999999E-3</v>
+        <v>2.8800000000000001E-4</v>
       </c>
       <c r="H77" s="13">
-        <v>3.7E-7</v>
+        <v>8.0000000000000002E-8</v>
       </c>
       <c r="I77" s="13">
         <v>0</v>
@@ -4956,7 +5039,7 @@
         <v>1</v>
       </c>
       <c r="K77" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L77" s="15">
         <v>0</v>
@@ -4975,26 +5058,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A78" s="10"/>
       <c r="B78" s="11"/>
       <c r="C78" s="12" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="D78" s="12" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="E78" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F78" s="13">
-        <v>3.0669999999999998E-3</v>
+        <v>2.4039999999999999E-3</v>
       </c>
       <c r="G78" s="13">
-        <v>1.7730000000000001E-3</v>
+        <v>2.0899999999999998E-3</v>
       </c>
       <c r="H78" s="13">
-        <v>3.5999999999999999E-7</v>
+        <v>5.5000000000000003E-7</v>
       </c>
       <c r="I78" s="13">
         <v>0</v>
@@ -5003,7 +5086,7 @@
         <v>1</v>
       </c>
       <c r="K78" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L78" s="15">
         <v>0</v>
@@ -5022,26 +5105,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A79" s="10"/>
       <c r="B79" s="11"/>
       <c r="C79" s="12" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E79" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F79" s="13">
-        <v>1.2359999999999999E-3</v>
+        <v>3.9439999999999996E-3</v>
       </c>
       <c r="G79" s="13">
-        <v>7.1500000000000003E-4</v>
+        <v>2.281E-3</v>
       </c>
       <c r="H79" s="13">
-        <v>1.4999999999999999E-7</v>
+        <v>4.5999999999999999E-7</v>
       </c>
       <c r="I79" s="13">
         <v>0</v>
@@ -5069,26 +5152,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A80" s="10"/>
       <c r="B80" s="11"/>
       <c r="C80" s="12" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F80" s="13">
-        <v>1.6080000000000001E-3</v>
+        <v>5.4289999999999998E-3</v>
       </c>
       <c r="G80" s="13">
-        <v>1.3979999999999999E-3</v>
+        <v>2.202E-3</v>
       </c>
       <c r="H80" s="13">
-        <v>3.7E-7</v>
+        <v>3.4999999999999998E-7</v>
       </c>
       <c r="I80" s="13">
         <v>0</v>
@@ -5097,7 +5180,7 @@
         <v>1</v>
       </c>
       <c r="K80" s="14">
-        <v>15.240315055798551</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L80" s="15">
         <v>0</v>
@@ -5116,26 +5199,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A81" s="10"/>
       <c r="B81" s="11"/>
       <c r="C81" s="12" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>179</v>
+        <v>163</v>
       </c>
       <c r="E81" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F81" s="13">
-        <v>1.0039999999999999E-3</v>
+        <v>6.2049999999999996E-3</v>
       </c>
       <c r="G81" s="13">
-        <v>5.8E-4</v>
+        <v>4.4320000000000002E-3</v>
       </c>
       <c r="H81" s="13">
-        <v>1.1999999999999999E-7</v>
+        <v>1E-8</v>
       </c>
       <c r="I81" s="13">
         <v>0</v>
@@ -5144,7 +5227,7 @@
         <v>1</v>
       </c>
       <c r="K81" s="14">
-        <v>11.63938142686286</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L81" s="15">
         <v>0</v>
@@ -5163,26 +5246,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A82" s="10"/>
       <c r="B82" s="11"/>
       <c r="C82" s="12" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E82" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F82" s="13">
-        <v>2.598E-3</v>
+        <v>2.1640000000000001E-3</v>
       </c>
       <c r="G82" s="13">
-        <v>1.5020000000000001E-3</v>
+        <v>1.882E-3</v>
       </c>
       <c r="H82" s="13">
-        <v>3.1E-7</v>
+        <v>4.8999999999999997E-7</v>
       </c>
       <c r="I82" s="13">
         <v>0</v>
@@ -5191,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="K82" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L82" s="15">
         <v>0</v>
@@ -5210,26 +5293,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="83" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A83" s="10"/>
       <c r="B83" s="11"/>
       <c r="C83" s="12" t="s">
-        <v>181</v>
+        <v>114</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="E83" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F83" s="13">
-        <v>2.369E-3</v>
+        <v>5.0280000000000004E-3</v>
       </c>
       <c r="G83" s="13">
-        <v>1.3699999999999999E-3</v>
+        <v>2.039E-3</v>
       </c>
       <c r="H83" s="13">
-        <v>2.8000000000000002E-7</v>
+        <v>3.3000000000000002E-7</v>
       </c>
       <c r="I83" s="13">
         <v>0</v>
@@ -5238,7 +5321,7 @@
         <v>1</v>
       </c>
       <c r="K83" s="14">
-        <v>11.63938142686286</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L83" s="15">
         <v>0</v>
@@ -5257,26 +5340,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="84" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="84" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A84" s="10"/>
       <c r="B84" s="11"/>
       <c r="C84" s="12" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="E84" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F84" s="13">
-        <v>1.7210000000000001E-3</v>
+        <v>2.0070000000000001E-3</v>
       </c>
       <c r="G84" s="13">
-        <v>9.9500000000000001E-4</v>
+        <v>1.745E-3</v>
       </c>
       <c r="H84" s="13">
-        <v>1.9999999999999999E-7</v>
+        <v>4.5999999999999999E-7</v>
       </c>
       <c r="I84" s="13">
         <v>0</v>
@@ -5285,7 +5368,7 @@
         <v>1</v>
       </c>
       <c r="K84" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L84" s="15">
         <v>0</v>
@@ -5304,26 +5387,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="85" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="85" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A85" s="10"/>
       <c r="B85" s="11"/>
       <c r="C85" s="12" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="E85" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F85" s="13">
-        <v>1.0070000000000001E-3</v>
+        <v>3.1670000000000001E-3</v>
       </c>
       <c r="G85" s="13">
-        <v>8.7600000000000004E-4</v>
+        <v>1.8309999999999999E-3</v>
       </c>
       <c r="H85" s="13">
-        <v>2.2999999999999999E-7</v>
+        <v>3.7E-7</v>
       </c>
       <c r="I85" s="13">
         <v>0</v>
@@ -5332,7 +5415,7 @@
         <v>1</v>
       </c>
       <c r="K85" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L85" s="15">
         <v>0</v>
@@ -5351,26 +5434,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="86" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="86" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A86" s="10"/>
       <c r="B86" s="11"/>
       <c r="C86" s="12" t="s">
-        <v>114</v>
+        <v>170</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="E86" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F86" s="13">
-        <v>1.433E-3</v>
+        <v>3.0669999999999998E-3</v>
       </c>
       <c r="G86" s="13">
-        <v>8.2899999999999998E-4</v>
+        <v>1.7730000000000001E-3</v>
       </c>
       <c r="H86" s="13">
-        <v>1.6999999999999999E-7</v>
+        <v>3.5999999999999999E-7</v>
       </c>
       <c r="I86" s="13">
         <v>0</v>
@@ -5398,26 +5481,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="87" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="87" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A87" s="10"/>
       <c r="B87" s="11"/>
       <c r="C87" s="12" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>145</v>
+        <v>173</v>
       </c>
       <c r="E87" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F87" s="13">
-        <v>9.6699999999999998E-4</v>
+        <v>1.2359999999999999E-3</v>
       </c>
       <c r="G87" s="13">
-        <v>5.5900000000000004E-4</v>
+        <v>7.1500000000000003E-4</v>
       </c>
       <c r="H87" s="13">
-        <v>1.1000000000000001E-7</v>
+        <v>1.4999999999999999E-7</v>
       </c>
       <c r="I87" s="13">
         <v>0</v>
@@ -5445,26 +5528,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="88" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A88" s="10"/>
       <c r="B88" s="11"/>
       <c r="C88" s="12" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>186</v>
+        <v>120</v>
       </c>
       <c r="E88" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F88" s="13">
-        <v>1.4269E-2</v>
+        <v>1.6080000000000001E-3</v>
       </c>
       <c r="G88" s="13">
-        <v>1.4037000000000001E-2</v>
+        <v>1.3979999999999999E-3</v>
       </c>
       <c r="H88" s="13">
-        <v>4.0000000000000001E-8</v>
+        <v>3.7E-7</v>
       </c>
       <c r="I88" s="13">
         <v>0</v>
@@ -5473,7 +5556,7 @@
         <v>1</v>
       </c>
       <c r="K88" s="14">
-        <v>12.366842766041779</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L88" s="15">
         <v>0</v>
@@ -5492,26 +5575,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="89" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="89" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A89" s="10"/>
       <c r="B89" s="11"/>
       <c r="C89" s="12" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
       <c r="E89" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F89" s="13">
-        <v>5.53E-4</v>
+        <v>1.0039999999999999E-3</v>
       </c>
       <c r="G89" s="13">
-        <v>4.8099999999999998E-4</v>
+        <v>5.8E-4</v>
       </c>
       <c r="H89" s="13">
-        <v>1.3E-7</v>
+        <v>1.1999999999999999E-7</v>
       </c>
       <c r="I89" s="13">
         <v>0</v>
@@ -5520,7 +5603,7 @@
         <v>1</v>
       </c>
       <c r="K89" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L89" s="15">
         <v>0</v>
@@ -5539,26 +5622,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="90" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="90" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A90" s="10"/>
       <c r="B90" s="11"/>
       <c r="C90" s="12" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E90" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F90" s="13">
-        <v>5.0100000000000003E-4</v>
+        <v>2.598E-3</v>
       </c>
       <c r="G90" s="13">
-        <v>4.3600000000000003E-4</v>
+        <v>1.5020000000000001E-3</v>
       </c>
       <c r="H90" s="13">
-        <v>1.1000000000000001E-7</v>
+        <v>3.1E-7</v>
       </c>
       <c r="I90" s="13">
         <v>0</v>
@@ -5567,7 +5650,7 @@
         <v>1</v>
       </c>
       <c r="K90" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L90" s="15">
         <v>0</v>
@@ -5586,26 +5669,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="91" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="91" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A91" s="10"/>
       <c r="B91" s="11"/>
       <c r="C91" s="12" t="s">
-        <v>155</v>
+        <v>178</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="E91" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F91" s="13">
-        <v>4.37E-4</v>
+        <v>2.369E-3</v>
       </c>
       <c r="G91" s="13">
-        <v>3.8000000000000002E-4</v>
+        <v>1.3699999999999999E-3</v>
       </c>
       <c r="H91" s="13">
-        <v>9.9999999999999995E-8</v>
+        <v>2.8000000000000002E-7</v>
       </c>
       <c r="I91" s="13">
         <v>0</v>
@@ -5614,7 +5697,7 @@
         <v>1</v>
       </c>
       <c r="K91" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L91" s="15">
         <v>0</v>
@@ -5633,26 +5716,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="92" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="92" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A92" s="10"/>
       <c r="B92" s="11"/>
       <c r="C92" s="12" t="s">
         <v>111</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
       <c r="E92" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F92" s="13">
-        <v>1.0150000000000001E-3</v>
+        <v>1.7210000000000001E-3</v>
       </c>
       <c r="G92" s="13">
-        <v>4.1199999999999999E-4</v>
+        <v>9.9500000000000001E-4</v>
       </c>
       <c r="H92" s="13">
-        <v>7.0000000000000005E-8</v>
+        <v>1.9999999999999999E-7</v>
       </c>
       <c r="I92" s="13">
         <v>0</v>
@@ -5661,7 +5744,7 @@
         <v>1</v>
       </c>
       <c r="K92" s="14">
-        <v>9.1296398066955522</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L92" s="15">
         <v>0</v>
@@ -5680,26 +5763,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="93" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="93" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A93" s="10"/>
       <c r="B93" s="11"/>
       <c r="C93" s="12" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>106</v>
+        <v>181</v>
       </c>
       <c r="E93" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F93" s="13">
-        <v>3.9899999999999999E-4</v>
+        <v>1.0070000000000001E-3</v>
       </c>
       <c r="G93" s="13">
-        <v>3.4699999999999998E-4</v>
+        <v>8.7600000000000004E-4</v>
       </c>
       <c r="H93" s="13">
-        <v>8.9999999999999999E-8</v>
+        <v>2.2999999999999999E-7</v>
       </c>
       <c r="I93" s="13">
         <v>0</v>
@@ -5727,26 +5810,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="94" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="94" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A94" s="10"/>
       <c r="B94" s="11"/>
       <c r="C94" s="12" t="s">
-        <v>193</v>
+        <v>111</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>125</v>
+        <v>182</v>
       </c>
       <c r="E94" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F94" s="13">
-        <v>4.6299999999999998E-4</v>
+        <v>1.433E-3</v>
       </c>
       <c r="G94" s="13">
-        <v>2.6800000000000001E-4</v>
+        <v>8.2899999999999998E-4</v>
       </c>
       <c r="H94" s="13">
-        <v>4.9999999999999998E-8</v>
+        <v>1.6999999999999999E-7</v>
       </c>
       <c r="I94" s="13">
         <v>0</v>
@@ -5774,26 +5857,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="95" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="95" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A95" s="10"/>
       <c r="B95" s="11"/>
       <c r="C95" s="12" t="s">
-        <v>118</v>
+        <v>183</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>193</v>
+        <v>142</v>
       </c>
       <c r="E95" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F95" s="13">
-        <v>1.16E-4</v>
+        <v>9.6699999999999998E-4</v>
       </c>
       <c r="G95" s="13">
-        <v>1.01E-4</v>
+        <v>5.5900000000000004E-4</v>
       </c>
       <c r="H95" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>1.1000000000000001E-7</v>
       </c>
       <c r="I95" s="13">
         <v>0</v>
@@ -5802,7 +5885,7 @@
         <v>1</v>
       </c>
       <c r="K95" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L95" s="15">
         <v>0</v>
@@ -5821,26 +5904,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="96" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A96" s="10"/>
       <c r="B96" s="11"/>
       <c r="C96" s="12" t="s">
-        <v>152</v>
+        <v>184</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="E96" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F96" s="13">
-        <v>2.34E-4</v>
+        <v>1.4269E-2</v>
       </c>
       <c r="G96" s="13">
-        <v>2.03E-4</v>
+        <v>1.4037000000000001E-2</v>
       </c>
       <c r="H96" s="13">
-        <v>4.9999999999999998E-8</v>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="I96" s="13">
         <v>0</v>
@@ -5849,7 +5932,7 @@
         <v>1</v>
       </c>
       <c r="K96" s="14">
-        <v>15.240315055798551</v>
+        <v>12.366842766041779</v>
       </c>
       <c r="L96" s="15">
         <v>0</v>
@@ -5868,26 +5951,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="97" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A97" s="10"/>
       <c r="B97" s="11"/>
       <c r="C97" s="12" t="s">
-        <v>133</v>
+        <v>185</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="E97" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F97" s="13">
-        <v>1.4300000000000001E-4</v>
+        <v>5.53E-4</v>
       </c>
       <c r="G97" s="13">
-        <v>1.25E-4</v>
+        <v>4.8099999999999998E-4</v>
       </c>
       <c r="H97" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>1.3E-7</v>
       </c>
       <c r="I97" s="13">
         <v>0</v>
@@ -5915,26 +5998,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="98" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A98" s="10"/>
       <c r="B98" s="11"/>
       <c r="C98" s="12" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D98" s="12" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="E98" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F98" s="13">
-        <v>1.8200000000000001E-4</v>
+        <v>5.0100000000000003E-4</v>
       </c>
       <c r="G98" s="13">
-        <v>1.05E-4</v>
+        <v>4.3600000000000003E-4</v>
       </c>
       <c r="H98" s="13">
-        <v>2E-8</v>
+        <v>1.1000000000000001E-7</v>
       </c>
       <c r="I98" s="13">
         <v>0</v>
@@ -5943,7 +6026,7 @@
         <v>1</v>
       </c>
       <c r="K98" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L98" s="15">
         <v>0</v>
@@ -5962,26 +6045,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="99" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A99" s="10"/>
       <c r="B99" s="11"/>
       <c r="C99" s="12" t="s">
-        <v>91</v>
+        <v>152</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E99" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F99" s="13">
-        <v>1.5696000000000002E-2</v>
+        <v>4.37E-4</v>
       </c>
       <c r="G99" s="13">
-        <v>1.1211E-2</v>
+        <v>3.8000000000000002E-4</v>
       </c>
       <c r="H99" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="I99" s="13">
         <v>0</v>
@@ -5990,7 +6073,7 @@
         <v>1</v>
       </c>
       <c r="K99" s="14">
-        <v>9.2751320745313386</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L99" s="15">
         <v>0</v>
@@ -6009,26 +6092,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A100" s="10"/>
       <c r="B100" s="11"/>
       <c r="C100" s="12" t="s">
-        <v>196</v>
+        <v>108</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E100" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F100" s="13">
-        <v>3.6003E-2</v>
+        <v>1.0150000000000001E-3</v>
       </c>
       <c r="G100" s="13">
-        <v>3.542E-2</v>
+        <v>4.1199999999999999E-4</v>
       </c>
       <c r="H100" s="13">
-        <v>9.9999999999999995E-8</v>
+        <v>7.0000000000000005E-8</v>
       </c>
       <c r="I100" s="13">
         <v>0</v>
@@ -6037,7 +6120,7 @@
         <v>1</v>
       </c>
       <c r="K100" s="14">
-        <v>12.366842766041779</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L100" s="15">
         <v>0</v>
@@ -6056,26 +6139,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="101" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A101" s="10"/>
       <c r="B101" s="11"/>
       <c r="C101" s="12" t="s">
-        <v>162</v>
+        <v>188</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>197</v>
+        <v>103</v>
       </c>
       <c r="E101" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F101" s="13">
-        <v>4.3748000000000002E-2</v>
+        <v>3.9899999999999999E-4</v>
       </c>
       <c r="G101" s="13">
-        <v>3.1248999999999999E-2</v>
+        <v>3.4699999999999998E-4</v>
       </c>
       <c r="H101" s="13">
-        <v>8.0000000000000002E-8</v>
+        <v>8.9999999999999999E-8</v>
       </c>
       <c r="I101" s="13">
         <v>0</v>
@@ -6084,7 +6167,7 @@
         <v>1</v>
       </c>
       <c r="K101" s="14">
-        <v>9.2751320745313386</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L101" s="15">
         <v>0</v>
@@ -6103,26 +6186,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="102" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="102" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A102" s="10"/>
       <c r="B102" s="11"/>
       <c r="C102" s="12" t="s">
-        <v>135</v>
+        <v>190</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>198</v>
+        <v>122</v>
       </c>
       <c r="E102" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F102" s="13">
-        <v>5.1159999999999999E-3</v>
+        <v>4.6299999999999998E-4</v>
       </c>
       <c r="G102" s="13">
-        <v>3.6540000000000001E-3</v>
+        <v>2.6800000000000001E-4</v>
       </c>
       <c r="H102" s="13">
-        <v>1E-8</v>
+        <v>4.9999999999999998E-8</v>
       </c>
       <c r="I102" s="13">
         <v>0</v>
@@ -6131,7 +6214,7 @@
         <v>1</v>
       </c>
       <c r="K102" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L102" s="15">
         <v>0</v>
@@ -6150,26 +6233,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A103" s="10"/>
       <c r="B103" s="11"/>
       <c r="C103" s="12" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E103" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F103" s="13">
-        <v>3.7416999999999999E-2</v>
+        <v>1.16E-4</v>
       </c>
       <c r="G103" s="13">
-        <v>2.6726E-2</v>
+        <v>1.01E-4</v>
       </c>
       <c r="H103" s="13">
-        <v>7.0000000000000005E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I103" s="13">
         <v>0</v>
@@ -6178,7 +6261,7 @@
         <v>1</v>
       </c>
       <c r="K103" s="14">
-        <v>9.2751320745313386</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L103" s="15">
         <v>0</v>
@@ -6197,26 +6280,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="104" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A104" s="10"/>
       <c r="B104" s="11"/>
       <c r="C104" s="12" t="s">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="E104" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F104" s="13">
-        <v>1.3061E-2</v>
+        <v>2.34E-4</v>
       </c>
       <c r="G104" s="13">
-        <v>9.3290000000000005E-3</v>
+        <v>2.03E-4</v>
       </c>
       <c r="H104" s="13">
-        <v>2E-8</v>
+        <v>4.9999999999999998E-8</v>
       </c>
       <c r="I104" s="13">
         <v>0</v>
@@ -6225,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="K104" s="14">
-        <v>9.2751320745313386</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L104" s="15">
         <v>0</v>
@@ -6244,26 +6327,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="105" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="105" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A105" s="10"/>
       <c r="B105" s="11"/>
       <c r="C105" s="12" t="s">
-        <v>201</v>
+        <v>130</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>202</v>
+        <v>148</v>
       </c>
       <c r="E105" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F105" s="13">
-        <v>6.6750000000000004E-3</v>
+        <v>1.4300000000000001E-4</v>
       </c>
       <c r="G105" s="13">
-        <v>2.6617999999999999E-2</v>
+        <v>1.25E-4</v>
       </c>
       <c r="H105" s="13">
-        <v>5.9999999999999995E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I105" s="13">
         <v>0</v>
@@ -6272,7 +6355,7 @@
         <v>1</v>
       </c>
       <c r="K105" s="14">
-        <v>6.1834213830208924</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L105" s="15">
         <v>0</v>
@@ -6291,26 +6374,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="106" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A106" s="10"/>
       <c r="B106" s="11"/>
       <c r="C106" s="12" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="E106" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F106" s="13">
-        <v>3.0641000000000002E-2</v>
+        <v>1.8200000000000001E-4</v>
       </c>
       <c r="G106" s="13">
-        <v>2.1885999999999999E-2</v>
+        <v>1.05E-4</v>
       </c>
       <c r="H106" s="13">
-        <v>5.9999999999999995E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I106" s="13">
         <v>0</v>
@@ -6319,7 +6402,7 @@
         <v>1</v>
       </c>
       <c r="K106" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L106" s="15">
         <v>0</v>
@@ -6338,23 +6421,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A107" s="10"/>
       <c r="B107" s="11"/>
       <c r="C107" s="12" t="s">
-        <v>204</v>
+        <v>88</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>169</v>
+        <v>193</v>
       </c>
       <c r="E107" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F107" s="13">
-        <v>1.4246999999999999E-2</v>
+        <v>1.5696000000000002E-2</v>
       </c>
       <c r="G107" s="13">
-        <v>1.0175999999999999E-2</v>
+        <v>1.1211E-2</v>
       </c>
       <c r="H107" s="13">
         <v>2.9999999999999997E-8</v>
@@ -6385,26 +6468,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="108" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A108" s="10"/>
       <c r="B108" s="11"/>
       <c r="C108" s="12" t="s">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="D108" s="12" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="E108" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F108" s="13">
-        <v>1.5499000000000001E-2</v>
+        <v>3.6003E-2</v>
       </c>
       <c r="G108" s="13">
-        <v>4.5999999999999999E-3</v>
+        <v>3.542E-2</v>
       </c>
       <c r="H108" s="13">
-        <v>1E-8</v>
+        <v>9.9999999999999995E-8</v>
       </c>
       <c r="I108" s="13">
         <v>0</v>
@@ -6413,7 +6496,7 @@
         <v>1</v>
       </c>
       <c r="K108" s="14">
-        <v>5.0922293742524998</v>
+        <v>12.366842766041779</v>
       </c>
       <c r="L108" s="15">
         <v>0</v>
@@ -6432,26 +6515,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="109" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A109" s="10"/>
       <c r="B109" s="11"/>
       <c r="C109" s="12" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="D109" s="12" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="E109" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F109" s="13">
-        <v>2.5180999999999999E-2</v>
+        <v>4.3748000000000002E-2</v>
       </c>
       <c r="G109" s="13">
-        <v>1.7985999999999999E-2</v>
+        <v>3.1248999999999999E-2</v>
       </c>
       <c r="H109" s="13">
-        <v>4.9999999999999998E-8</v>
+        <v>8.0000000000000002E-8</v>
       </c>
       <c r="I109" s="13">
         <v>0</v>
@@ -6479,26 +6562,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="110" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A110" s="10"/>
       <c r="B110" s="11"/>
       <c r="C110" s="12" t="s">
-        <v>208</v>
+        <v>132</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="E110" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F110" s="13">
-        <v>4.3543999999999999E-2</v>
+        <v>5.1159999999999999E-3</v>
       </c>
       <c r="G110" s="13">
-        <v>1.7364000000000001E-2</v>
+        <v>3.6540000000000001E-3</v>
       </c>
       <c r="H110" s="13">
-        <v>4.0000000000000001E-8</v>
+        <v>1E-8</v>
       </c>
       <c r="I110" s="13">
         <v>0</v>
@@ -6507,7 +6590,7 @@
         <v>1</v>
       </c>
       <c r="K110" s="14">
-        <v>6.1834213830208924</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L110" s="15">
         <v>0</v>
@@ -6526,26 +6609,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="111" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A111" s="10"/>
       <c r="B111" s="11"/>
       <c r="C111" s="12" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="E111" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F111" s="13">
-        <v>2.1132000000000001E-2</v>
+        <v>3.7416999999999999E-2</v>
       </c>
       <c r="G111" s="13">
-        <v>1.5094E-2</v>
+        <v>2.6726E-2</v>
       </c>
       <c r="H111" s="13">
-        <v>4.0000000000000001E-8</v>
+        <v>7.0000000000000005E-8</v>
       </c>
       <c r="I111" s="13">
         <v>0</v>
@@ -6573,26 +6656,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="112" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A112" s="10"/>
       <c r="B112" s="11"/>
       <c r="C112" s="12" t="s">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="E112" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F112" s="13">
-        <v>2.0759E-2</v>
+        <v>1.3061E-2</v>
       </c>
       <c r="G112" s="13">
-        <v>1.4827999999999999E-2</v>
+        <v>9.3290000000000005E-3</v>
       </c>
       <c r="H112" s="13">
-        <v>4.0000000000000001E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I112" s="13">
         <v>0</v>
@@ -6620,26 +6703,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A113" s="10"/>
       <c r="B113" s="11"/>
       <c r="C113" s="12" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="E113" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F113" s="13">
-        <v>1.9491999999999999E-2</v>
+        <v>6.6750000000000004E-3</v>
       </c>
       <c r="G113" s="13">
-        <v>1.3923E-2</v>
+        <v>2.6617999999999999E-2</v>
       </c>
       <c r="H113" s="13">
-        <v>4.0000000000000001E-8</v>
+        <v>5.9999999999999995E-8</v>
       </c>
       <c r="I113" s="13">
         <v>0</v>
@@ -6648,7 +6731,7 @@
         <v>1</v>
       </c>
       <c r="K113" s="14">
-        <v>9.8207280789155327</v>
+        <v>6.1834213830208924</v>
       </c>
       <c r="L113" s="15">
         <v>0</v>
@@ -6667,26 +6750,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A114" s="10"/>
       <c r="B114" s="11"/>
       <c r="C114" s="12" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="E114" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F114" s="13">
-        <v>1.7711000000000001E-2</v>
+        <v>3.0641000000000002E-2</v>
       </c>
       <c r="G114" s="13">
-        <v>1.2651000000000001E-2</v>
+        <v>2.1885999999999999E-2</v>
       </c>
       <c r="H114" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>5.9999999999999995E-8</v>
       </c>
       <c r="I114" s="13">
         <v>0</v>
@@ -6714,26 +6797,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A115" s="10"/>
       <c r="B115" s="11"/>
       <c r="C115" s="12" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D115" s="12" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E115" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F115" s="13">
-        <v>2.5360000000000001E-3</v>
+        <v>1.4246999999999999E-2</v>
       </c>
       <c r="G115" s="13">
-        <v>1.812E-3</v>
+        <v>1.0175999999999999E-2</v>
       </c>
       <c r="H115" s="13">
-        <v>1E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I115" s="13">
         <v>0</v>
@@ -6761,23 +6844,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A116" s="10"/>
       <c r="B116" s="11"/>
       <c r="C116" s="12" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="E116" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F116" s="13">
-        <v>2.5049999999999998E-3</v>
+        <v>1.5499000000000001E-2</v>
       </c>
       <c r="G116" s="13">
-        <v>1.789E-3</v>
+        <v>4.5999999999999999E-3</v>
       </c>
       <c r="H116" s="13">
         <v>1E-8</v>
@@ -6789,7 +6872,7 @@
         <v>1</v>
       </c>
       <c r="K116" s="14">
-        <v>9.2751320745313386</v>
+        <v>5.0922293742524998</v>
       </c>
       <c r="L116" s="15">
         <v>0</v>
@@ -6808,26 +6891,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="11"/>
       <c r="C117" s="12" t="s">
-        <v>143</v>
+        <v>203</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="E117" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F117" s="13">
-        <v>1.5768999999999998E-2</v>
+        <v>2.5180999999999999E-2</v>
       </c>
       <c r="G117" s="13">
-        <v>1.1264E-2</v>
+        <v>1.7985999999999999E-2</v>
       </c>
       <c r="H117" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>4.9999999999999998E-8</v>
       </c>
       <c r="I117" s="13">
         <v>0</v>
@@ -6855,26 +6938,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A118" s="10"/>
       <c r="B118" s="11"/>
       <c r="C118" s="12" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="E118" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F118" s="13">
-        <v>1.6197E-2</v>
+        <v>4.3543999999999999E-2</v>
       </c>
       <c r="G118" s="13">
-        <v>1.1568999999999999E-2</v>
+        <v>1.7364000000000001E-2</v>
       </c>
       <c r="H118" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="I118" s="13">
         <v>0</v>
@@ -6883,7 +6966,7 @@
         <v>1</v>
       </c>
       <c r="K118" s="14">
-        <v>9.2751320745313386</v>
+        <v>6.1834213830208924</v>
       </c>
       <c r="L118" s="15">
         <v>0</v>
@@ -6902,26 +6985,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A119" s="10"/>
       <c r="B119" s="11"/>
       <c r="C119" s="12" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="E119" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F119" s="13">
-        <v>9.6100000000000005E-4</v>
+        <v>2.1132000000000001E-2</v>
       </c>
       <c r="G119" s="13">
-        <v>6.87E-4</v>
+        <v>1.5094E-2</v>
       </c>
       <c r="H119" s="13">
-        <v>1E-8</v>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="I119" s="13">
         <v>0</v>
@@ -6949,26 +7032,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A120" s="10"/>
       <c r="B120" s="11"/>
       <c r="C120" s="12" t="s">
-        <v>210</v>
+        <v>166</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="E120" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F120" s="13">
-        <v>1.4696000000000001E-2</v>
+        <v>2.0759E-2</v>
       </c>
       <c r="G120" s="13">
-        <v>1.0496999999999999E-2</v>
+        <v>1.4827999999999999E-2</v>
       </c>
       <c r="H120" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="I120" s="13">
         <v>0</v>
@@ -6996,26 +7079,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A121" s="10"/>
       <c r="B121" s="11"/>
       <c r="C121" s="12" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="E121" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F121" s="13">
-        <v>1.4619999999999999E-2</v>
+        <v>1.9491999999999999E-2</v>
       </c>
       <c r="G121" s="13">
-        <v>1.0442999999999999E-2</v>
+        <v>1.3923E-2</v>
       </c>
       <c r="H121" s="13">
-        <v>2.9999999999999997E-8</v>
+        <v>4.0000000000000001E-8</v>
       </c>
       <c r="I121" s="13">
         <v>0</v>
@@ -7024,7 +7107,7 @@
         <v>1</v>
       </c>
       <c r="K121" s="14">
-        <v>9.2751320745313386</v>
+        <v>9.8207280789155327</v>
       </c>
       <c r="L121" s="15">
         <v>0</v>
@@ -7043,26 +7126,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A122" s="10"/>
       <c r="B122" s="11"/>
       <c r="C122" s="12" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="E122" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F122" s="13">
-        <v>9.9480000000000002E-3</v>
+        <v>1.7711000000000001E-2</v>
       </c>
       <c r="G122" s="13">
-        <v>7.1060000000000003E-3</v>
+        <v>1.2651000000000001E-2</v>
       </c>
       <c r="H122" s="13">
-        <v>2E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I122" s="13">
         <v>0</v>
@@ -7090,26 +7173,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A123" s="10"/>
       <c r="B123" s="11"/>
       <c r="C123" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="E123" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F123" s="13">
-        <v>1.2158E-2</v>
+        <v>2.5360000000000001E-3</v>
       </c>
       <c r="G123" s="13">
-        <v>8.6840000000000007E-3</v>
+        <v>1.812E-3</v>
       </c>
       <c r="H123" s="13">
-        <v>2E-8</v>
+        <v>1E-8</v>
       </c>
       <c r="I123" s="13">
         <v>0</v>
@@ -7118,7 +7201,7 @@
         <v>1</v>
       </c>
       <c r="K123" s="14">
-        <v>9.8207280789155327</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L123" s="15">
         <v>0</v>
@@ -7137,23 +7220,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="124" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="124" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A124" s="10"/>
       <c r="B124" s="11"/>
       <c r="C124" s="12" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="E124" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F124" s="13">
-        <v>1.1249999999999999E-3</v>
+        <v>2.5049999999999998E-3</v>
       </c>
       <c r="G124" s="13">
-        <v>8.03E-4</v>
+        <v>1.789E-3</v>
       </c>
       <c r="H124" s="13">
         <v>1E-8</v>
@@ -7165,7 +7248,7 @@
         <v>1</v>
       </c>
       <c r="K124" s="14">
-        <v>9.8207280789155327</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L124" s="15">
         <v>0</v>
@@ -7184,26 +7267,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A125" s="10"/>
       <c r="B125" s="11"/>
       <c r="C125" s="12" t="s">
-        <v>208</v>
+        <v>140</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E125" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F125" s="13">
-        <v>1.1812E-2</v>
+        <v>1.5768999999999998E-2</v>
       </c>
       <c r="G125" s="13">
-        <v>8.4370000000000001E-3</v>
+        <v>1.1264E-2</v>
       </c>
       <c r="H125" s="13">
-        <v>2E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I125" s="13">
         <v>0</v>
@@ -7231,26 +7314,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A126" s="10"/>
       <c r="B126" s="11"/>
       <c r="C126" s="12" t="s">
-        <v>124</v>
+        <v>215</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="E126" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F126" s="13">
-        <v>1.1622E-2</v>
+        <v>1.6197E-2</v>
       </c>
       <c r="G126" s="13">
-        <v>8.3020000000000004E-3</v>
+        <v>1.1568999999999999E-2</v>
       </c>
       <c r="H126" s="13">
-        <v>2E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I126" s="13">
         <v>0</v>
@@ -7278,26 +7361,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A127" s="10"/>
       <c r="B127" s="11"/>
       <c r="C127" s="12" t="s">
-        <v>109</v>
+        <v>215</v>
       </c>
       <c r="D127" s="12" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="E127" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F127" s="13">
-        <v>1.1495E-2</v>
+        <v>9.6100000000000005E-4</v>
       </c>
       <c r="G127" s="13">
-        <v>8.2109999999999995E-3</v>
+        <v>6.87E-4</v>
       </c>
       <c r="H127" s="13">
-        <v>2E-8</v>
+        <v>1E-8</v>
       </c>
       <c r="I127" s="13">
         <v>0</v>
@@ -7325,26 +7408,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A128" s="10"/>
       <c r="B128" s="11"/>
       <c r="C128" s="12" t="s">
-        <v>167</v>
+        <v>207</v>
       </c>
       <c r="D128" s="12" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="E128" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F128" s="13">
-        <v>1.0005999999999999E-2</v>
+        <v>1.4696000000000001E-2</v>
       </c>
       <c r="G128" s="13">
-        <v>7.1469999999999997E-3</v>
+        <v>1.0496999999999999E-2</v>
       </c>
       <c r="H128" s="13">
-        <v>2E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I128" s="13">
         <v>0</v>
@@ -7372,26 +7455,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A129" s="10"/>
       <c r="B129" s="11"/>
       <c r="C129" s="12" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="D129" s="12" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="E129" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F129" s="13">
-        <v>1.7957000000000001E-2</v>
+        <v>1.4619999999999999E-2</v>
       </c>
       <c r="G129" s="13">
-        <v>7.1609999999999998E-3</v>
+        <v>1.0442999999999999E-2</v>
       </c>
       <c r="H129" s="13">
-        <v>2E-8</v>
+        <v>2.9999999999999997E-8</v>
       </c>
       <c r="I129" s="13">
         <v>0</v>
@@ -7400,7 +7483,7 @@
         <v>1</v>
       </c>
       <c r="K129" s="14">
-        <v>6.1834213830208924</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L129" s="15">
         <v>0</v>
@@ -7419,26 +7502,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A130" s="10"/>
       <c r="B130" s="11"/>
       <c r="C130" s="12" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D130" s="12" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E130" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F130" s="13">
-        <v>1.068E-2</v>
+        <v>9.9480000000000002E-3</v>
       </c>
       <c r="G130" s="13">
-        <v>5.8100000000000001E-3</v>
+        <v>7.1060000000000003E-3</v>
       </c>
       <c r="H130" s="13">
-        <v>1E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I130" s="13">
         <v>0</v>
@@ -7447,7 +7530,7 @@
         <v>1</v>
       </c>
       <c r="K130" s="14">
-        <v>7.6383440613787483</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L130" s="15">
         <v>0</v>
@@ -7466,26 +7549,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A131" s="10"/>
       <c r="B131" s="11"/>
       <c r="C131" s="12" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="D131" s="12" t="s">
-        <v>228</v>
+        <v>170</v>
       </c>
       <c r="E131" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F131" s="13">
-        <v>1.0522E-2</v>
+        <v>1.2158E-2</v>
       </c>
       <c r="G131" s="13">
-        <v>5.7239999999999999E-3</v>
+        <v>8.6840000000000007E-3</v>
       </c>
       <c r="H131" s="13">
-        <v>1E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I131" s="13">
         <v>0</v>
@@ -7494,7 +7577,7 @@
         <v>1</v>
       </c>
       <c r="K131" s="14">
-        <v>7.6383440613787483</v>
+        <v>9.8207280789155327</v>
       </c>
       <c r="L131" s="15">
         <v>0</v>
@@ -7513,23 +7596,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A132" s="10"/>
       <c r="B132" s="11"/>
       <c r="C132" s="12" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="D132" s="12" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="E132" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F132" s="13">
-        <v>5.3689999999999996E-3</v>
+        <v>1.1249999999999999E-3</v>
       </c>
       <c r="G132" s="13">
-        <v>3.8349999999999999E-3</v>
+        <v>8.03E-4</v>
       </c>
       <c r="H132" s="13">
         <v>1E-8</v>
@@ -7541,7 +7624,7 @@
         <v>1</v>
       </c>
       <c r="K132" s="14">
-        <v>9.2751320745313386</v>
+        <v>9.8207280789155327</v>
       </c>
       <c r="L132" s="15">
         <v>0</v>
@@ -7560,26 +7643,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A133" s="10"/>
       <c r="B133" s="11"/>
       <c r="C133" s="12" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="D133" s="12" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="E133" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F133" s="13">
-        <v>8.3960000000000007E-3</v>
+        <v>1.1812E-2</v>
       </c>
       <c r="G133" s="13">
-        <v>3.3479999999999998E-3</v>
+        <v>8.4370000000000001E-3</v>
       </c>
       <c r="H133" s="13">
-        <v>1E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I133" s="13">
         <v>0</v>
@@ -7588,7 +7671,7 @@
         <v>1</v>
       </c>
       <c r="K133" s="14">
-        <v>6.1834213830208924</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L133" s="15">
         <v>0</v>
@@ -7607,26 +7690,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A134" s="10"/>
       <c r="B134" s="11"/>
       <c r="C134" s="12" t="s">
-        <v>215</v>
+        <v>121</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>234</v>
+        <v>207</v>
       </c>
       <c r="E134" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F134" s="13">
-        <v>3.1800000000000001E-3</v>
+        <v>1.1622E-2</v>
       </c>
       <c r="G134" s="13">
-        <v>2.2720000000000001E-3</v>
+        <v>8.3020000000000004E-3</v>
       </c>
       <c r="H134" s="13">
-        <v>1E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I134" s="13">
         <v>0</v>
@@ -7654,26 +7737,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A135" s="10"/>
       <c r="B135" s="11"/>
       <c r="C135" s="12" t="s">
-        <v>228</v>
+        <v>106</v>
       </c>
       <c r="D135" s="12" t="s">
-        <v>235</v>
+        <v>198</v>
       </c>
       <c r="E135" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F135" s="13">
-        <v>4.6979999999999999E-3</v>
+        <v>1.1495E-2</v>
       </c>
       <c r="G135" s="13">
-        <v>1.874E-3</v>
+        <v>8.2109999999999995E-3</v>
       </c>
       <c r="H135" s="13">
-        <v>1E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I135" s="13">
         <v>0</v>
@@ -7682,7 +7765,7 @@
         <v>1</v>
       </c>
       <c r="K135" s="14">
-        <v>6.1834213830208924</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L135" s="15">
         <v>0</v>
@@ -7701,26 +7784,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A136" s="10"/>
       <c r="B136" s="11"/>
       <c r="C136" s="12" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D136" s="12" t="s">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="E136" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F136" s="13">
-        <v>4.4939999999999997E-3</v>
+        <v>1.0005999999999999E-2</v>
       </c>
       <c r="G136" s="13">
-        <v>1.792E-3</v>
+        <v>7.1469999999999997E-3</v>
       </c>
       <c r="H136" s="13">
-        <v>1E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I136" s="13">
         <v>0</v>
@@ -7729,7 +7812,7 @@
         <v>1</v>
       </c>
       <c r="K136" s="14">
-        <v>6.1834213830208924</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L136" s="15">
         <v>0</v>
@@ -7748,26 +7831,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A137" s="10"/>
       <c r="B137" s="11"/>
       <c r="C137" s="12" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="D137" s="12" t="s">
-        <v>149</v>
+        <v>224</v>
       </c>
       <c r="E137" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F137" s="13">
-        <v>1.023E-3</v>
+        <v>1.7957000000000001E-2</v>
       </c>
       <c r="G137" s="13">
-        <v>7.3099999999999999E-4</v>
+        <v>7.1609999999999998E-3</v>
       </c>
       <c r="H137" s="13">
-        <v>1E-8</v>
+        <v>2E-8</v>
       </c>
       <c r="I137" s="13">
         <v>0</v>
@@ -7776,7 +7859,7 @@
         <v>1</v>
       </c>
       <c r="K137" s="14">
-        <v>9.2751320745313386</v>
+        <v>6.1834213830208924</v>
       </c>
       <c r="L137" s="15">
         <v>0</v>
@@ -7795,26 +7878,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A138" s="10"/>
       <c r="B138" s="11"/>
       <c r="C138" s="12" t="s">
-        <v>78</v>
+        <v>225</v>
       </c>
       <c r="D138" s="12" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="E138" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F138" s="13">
-        <v>2.1628000000000001E-2</v>
+        <v>1.068E-2</v>
       </c>
       <c r="G138" s="13">
-        <v>1.8799E-2</v>
+        <v>5.8100000000000001E-3</v>
       </c>
       <c r="H138" s="13">
-        <v>4.9400000000000001E-6</v>
+        <v>1E-8</v>
       </c>
       <c r="I138" s="13">
         <v>0</v>
@@ -7823,7 +7906,7 @@
         <v>1</v>
       </c>
       <c r="K138" s="14">
-        <v>15.240315055798551</v>
+        <v>7.6383440613787483</v>
       </c>
       <c r="L138" s="15">
         <v>0</v>
@@ -7842,26 +7925,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A139" s="10"/>
       <c r="B139" s="11"/>
       <c r="C139" s="12" t="s">
-        <v>81</v>
+        <v>227</v>
       </c>
       <c r="D139" s="12" t="s">
-        <v>238</v>
+        <v>225</v>
       </c>
       <c r="E139" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F139" s="13">
-        <v>2.163E-2</v>
+        <v>1.0522E-2</v>
       </c>
       <c r="G139" s="13">
-        <v>1.8800999999999998E-2</v>
+        <v>5.7239999999999999E-3</v>
       </c>
       <c r="H139" s="13">
-        <v>1.237454545454545E-6</v>
+        <v>1E-8</v>
       </c>
       <c r="I139" s="13">
         <v>0</v>
@@ -7870,7 +7953,7 @@
         <v>1</v>
       </c>
       <c r="K139" s="14">
-        <v>15.240315055798551</v>
+        <v>7.6383440613787483</v>
       </c>
       <c r="L139" s="15">
         <v>0</v>
@@ -7889,26 +7972,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A140" s="10"/>
       <c r="B140" s="11"/>
       <c r="C140" s="12" t="s">
-        <v>165</v>
+        <v>228</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>130</v>
+        <v>229</v>
       </c>
       <c r="E140" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F140" s="13">
-        <v>8.990999999999999E-3</v>
+        <v>5.3689999999999996E-3</v>
       </c>
       <c r="G140" s="13">
-        <v>7.816E-3</v>
+        <v>3.8349999999999999E-3</v>
       </c>
       <c r="H140" s="13">
-        <v>9.9512195121951218E-9</v>
+        <v>1E-8</v>
       </c>
       <c r="I140" s="13">
         <v>0</v>
@@ -7917,7 +8000,7 @@
         <v>1</v>
       </c>
       <c r="K140" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L140" s="15">
         <v>0</v>
@@ -7936,26 +8019,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A141" s="10"/>
       <c r="B141" s="11"/>
       <c r="C141" s="12" t="s">
-        <v>239</v>
+        <v>209</v>
       </c>
       <c r="D141" s="12" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="E141" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F141" s="13">
-        <v>1.7922E-2</v>
+        <v>8.3960000000000007E-3</v>
       </c>
       <c r="G141" s="13">
-        <v>1.0362E-2</v>
+        <v>3.3479999999999998E-3</v>
       </c>
       <c r="H141" s="13">
-        <v>3.9687203791469199E-7</v>
+        <v>1E-8</v>
       </c>
       <c r="I141" s="13">
         <v>0</v>
@@ -7964,7 +8047,7 @@
         <v>1</v>
       </c>
       <c r="K141" s="14">
-        <v>11.63938142686286</v>
+        <v>6.1834213830208924</v>
       </c>
       <c r="L141" s="15">
         <v>0</v>
@@ -7983,26 +8066,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A142" s="10"/>
       <c r="B142" s="11"/>
       <c r="C142" s="12" t="s">
-        <v>139</v>
+        <v>212</v>
       </c>
       <c r="D142" s="12" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="E142" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F142" s="13">
-        <v>1.3272000000000001E-2</v>
+        <v>3.1800000000000001E-3</v>
       </c>
       <c r="G142" s="13">
-        <v>7.6730000000000001E-3</v>
+        <v>2.2720000000000001E-3</v>
       </c>
       <c r="H142" s="13">
-        <v>2.0307692307692311E-7</v>
+        <v>1E-8</v>
       </c>
       <c r="I142" s="13">
         <v>0</v>
@@ -8011,7 +8094,7 @@
         <v>1</v>
       </c>
       <c r="K142" s="14">
-        <v>11.63938142686286</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L142" s="15">
         <v>0</v>
@@ -8030,26 +8113,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A143" s="10"/>
       <c r="B143" s="11"/>
       <c r="C143" s="12" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="D143" s="12" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="E143" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F143" s="13">
-        <v>1.3421000000000001E-2</v>
+        <v>4.6979999999999999E-3</v>
       </c>
       <c r="G143" s="13">
-        <v>1.1665999999999999E-2</v>
+        <v>1.874E-3</v>
       </c>
       <c r="H143" s="13">
-        <v>7.6684039087947864E-7</v>
+        <v>1E-8</v>
       </c>
       <c r="I143" s="13">
         <v>0</v>
@@ -8058,7 +8141,7 @@
         <v>1</v>
       </c>
       <c r="K143" s="14">
-        <v>15.240315055798551</v>
+        <v>6.1834213830208924</v>
       </c>
       <c r="L143" s="15">
         <v>0</v>
@@ -8077,26 +8160,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A144" s="10"/>
       <c r="B144" s="11"/>
       <c r="C144" s="12" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E144" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F144" s="13">
-        <v>1.0328E-2</v>
+        <v>4.4939999999999997E-3</v>
       </c>
       <c r="G144" s="13">
-        <v>8.9779999999999999E-3</v>
+        <v>1.792E-3</v>
       </c>
       <c r="H144" s="13">
-        <v>5.7957805907172999E-7</v>
+        <v>1E-8</v>
       </c>
       <c r="I144" s="13">
         <v>0</v>
@@ -8105,7 +8188,7 @@
         <v>1</v>
       </c>
       <c r="K144" s="14">
-        <v>15.240315055798551</v>
+        <v>6.1834213830208924</v>
       </c>
       <c r="L144" s="15">
         <v>0</v>
@@ -8124,26 +8207,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="145" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="145" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A145" s="10"/>
       <c r="B145" s="11"/>
       <c r="C145" s="12" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="D145" s="12" t="s">
-        <v>244</v>
+        <v>146</v>
       </c>
       <c r="E145" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F145" s="13">
-        <v>5.339E-3</v>
+        <v>1.023E-3</v>
       </c>
       <c r="G145" s="13">
-        <v>3.0869999999999999E-3</v>
+        <v>7.3099999999999999E-4</v>
       </c>
       <c r="H145" s="13">
-        <v>6.2222222222222228E-8</v>
+        <v>1E-8</v>
       </c>
       <c r="I145" s="13">
         <v>0</v>
@@ -8152,7 +8235,7 @@
         <v>1</v>
       </c>
       <c r="K145" s="14">
-        <v>11.63938142686286</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L145" s="15">
         <v>0</v>
@@ -8171,26 +8254,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="146" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="146" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A146" s="10"/>
       <c r="B146" s="11"/>
       <c r="C146" s="12" t="s">
-        <v>164</v>
+        <v>78</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="E146" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F146" s="13">
-        <v>9.3530000000000002E-3</v>
+        <v>2.1628000000000001E-2</v>
       </c>
       <c r="G146" s="13">
-        <v>5.4079999999999996E-3</v>
+        <v>1.8799E-2</v>
       </c>
       <c r="H146" s="13">
-        <v>2.7490909090909092E-7</v>
+        <v>4.9400000000000001E-6</v>
       </c>
       <c r="I146" s="13">
         <v>0</v>
@@ -8199,7 +8282,7 @@
         <v>1</v>
       </c>
       <c r="K146" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L146" s="15">
         <v>0</v>
@@ -8218,26 +8301,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="147" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A147" s="10"/>
       <c r="B147" s="11"/>
       <c r="C147" s="12" t="s">
-        <v>137</v>
+        <v>259</v>
       </c>
       <c r="D147" s="12" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E147" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F147" s="13">
-        <v>9.6669999999999985E-3</v>
+        <v>2.163E-2</v>
       </c>
       <c r="G147" s="13">
-        <v>5.5880000000000001E-3</v>
+        <v>1.8800999999999998E-2</v>
       </c>
       <c r="H147" s="13">
-        <v>1.1150097465886939E-7</v>
+        <v>1.237454545454545E-6</v>
       </c>
       <c r="I147" s="13">
         <v>0</v>
@@ -8246,7 +8329,7 @@
         <v>1</v>
       </c>
       <c r="K147" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L147" s="15">
         <v>0</v>
@@ -8265,26 +8348,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="148" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="148" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A148" s="10"/>
       <c r="B148" s="11"/>
       <c r="C148" s="12" t="s">
-        <v>189</v>
+        <v>162</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>247</v>
+        <v>127</v>
       </c>
       <c r="E148" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F148" s="13">
-        <v>7.7619999999999998E-3</v>
+        <v>8.990999999999999E-3</v>
       </c>
       <c r="G148" s="13">
-        <v>4.4879999999999998E-3</v>
+        <v>7.816E-3</v>
       </c>
       <c r="H148" s="13">
-        <v>2.1163043478260869E-7</v>
+        <v>9.9512195121951218E-9</v>
       </c>
       <c r="I148" s="13">
         <v>0</v>
@@ -8293,7 +8376,7 @@
         <v>1</v>
       </c>
       <c r="K148" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L148" s="15">
         <v>0</v>
@@ -8312,26 +8395,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="149" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="149" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A149" s="10"/>
       <c r="B149" s="11"/>
       <c r="C149" s="12" t="s">
-        <v>82</v>
+        <v>235</v>
       </c>
       <c r="D149" s="12" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="E149" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F149" s="13">
-        <v>9.1520000000000004E-3</v>
+        <v>1.7922E-2</v>
       </c>
       <c r="G149" s="13">
-        <v>5.2919999999999998E-3</v>
+        <v>1.0362E-2</v>
       </c>
       <c r="H149" s="13">
-        <v>9.9420625724217845E-8</v>
+        <v>3.9687203791469199E-7</v>
       </c>
       <c r="I149" s="13">
         <v>0</v>
@@ -8359,26 +8442,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="150" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A150" s="10"/>
       <c r="B150" s="11"/>
       <c r="C150" s="12" t="s">
-        <v>249</v>
+        <v>136</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>95</v>
+        <v>237</v>
       </c>
       <c r="E150" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F150" s="13">
-        <v>8.2290000000000002E-3</v>
+        <v>1.3272000000000001E-2</v>
       </c>
       <c r="G150" s="13">
-        <v>7.1540000000000006E-3</v>
+        <v>7.6730000000000001E-3</v>
       </c>
       <c r="H150" s="13">
-        <v>1.666981132075472E-7</v>
+        <v>2.0307692307692311E-7</v>
       </c>
       <c r="I150" s="13">
         <v>0</v>
@@ -8387,7 +8470,7 @@
         <v>1</v>
       </c>
       <c r="K150" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L150" s="15">
         <v>0</v>
@@ -8406,26 +8489,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="151" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A151" s="10"/>
       <c r="B151" s="11"/>
       <c r="C151" s="12" t="s">
-        <v>87</v>
+        <v>238</v>
       </c>
       <c r="D151" s="12" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="E151" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F151" s="13">
-        <v>1.5865000000000001E-2</v>
+        <v>1.3421000000000001E-2</v>
       </c>
       <c r="G151" s="13">
-        <v>6.4349999999999997E-3</v>
+        <v>1.1665999999999999E-2</v>
       </c>
       <c r="H151" s="13">
-        <v>1.552884615384615E-7</v>
+        <v>7.6684039087947864E-7</v>
       </c>
       <c r="I151" s="13">
         <v>0</v>
@@ -8434,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="K151" s="14">
-        <v>9.1296398066955522</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L151" s="15">
         <v>0</v>
@@ -8453,26 +8536,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="152" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="152" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A152" s="10"/>
       <c r="B152" s="11"/>
       <c r="C152" s="12" t="s">
-        <v>246</v>
+        <v>180</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>140</v>
+        <v>235</v>
       </c>
       <c r="E152" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F152" s="13">
-        <v>9.389999999999999E-3</v>
+        <v>1.0328E-2</v>
       </c>
       <c r="G152" s="13">
-        <v>5.4300000000000008E-3</v>
+        <v>8.9779999999999999E-3</v>
       </c>
       <c r="H152" s="13">
-        <v>9.5593220338983041E-8</v>
+        <v>5.7957805907172999E-7</v>
       </c>
       <c r="I152" s="13">
         <v>0</v>
@@ -8481,7 +8564,7 @@
         <v>1</v>
       </c>
       <c r="K152" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L152" s="15">
         <v>0</v>
@@ -8500,26 +8583,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="153" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="153" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A153" s="10"/>
       <c r="B153" s="11"/>
       <c r="C153" s="12" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="D153" s="12" t="s">
-        <v>175</v>
+        <v>240</v>
       </c>
       <c r="E153" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F153" s="13">
-        <v>6.3359999999999996E-3</v>
+        <v>5.339E-3</v>
       </c>
       <c r="G153" s="13">
-        <v>2.5699999999999998E-3</v>
+        <v>3.0869999999999999E-3</v>
       </c>
       <c r="H153" s="13">
-        <v>8.8780487804878061E-8</v>
+        <v>6.2222222222222228E-8</v>
       </c>
       <c r="I153" s="13">
         <v>0</v>
@@ -8528,7 +8611,7 @@
         <v>1</v>
       </c>
       <c r="K153" s="14">
-        <v>9.1296398066955522</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L153" s="15">
         <v>0</v>
@@ -8547,26 +8630,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="154" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="154" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A154" s="10"/>
       <c r="B154" s="11"/>
       <c r="C154" s="12" t="s">
-        <v>252</v>
+        <v>161</v>
       </c>
       <c r="D154" s="12" t="s">
-        <v>115</v>
+        <v>241</v>
       </c>
       <c r="E154" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F154" s="13">
-        <v>4.9570999999999997E-2</v>
+        <v>9.3530000000000002E-3</v>
       </c>
       <c r="G154" s="13">
-        <v>3.5409000000000003E-2</v>
+        <v>5.4079999999999996E-3</v>
       </c>
       <c r="H154" s="13">
-        <v>8.8888888888888885E-9</v>
+        <v>2.7490909090909092E-7</v>
       </c>
       <c r="I154" s="13">
         <v>0</v>
@@ -8575,7 +8658,7 @@
         <v>1</v>
       </c>
       <c r="K154" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L154" s="15">
         <v>0</v>
@@ -8594,26 +8677,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="155" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="155" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A155" s="10"/>
       <c r="B155" s="11"/>
       <c r="C155" s="12" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="D155" s="12" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E155" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F155" s="13">
-        <v>6.2004999999999998E-2</v>
+        <v>9.6669999999999985E-3</v>
       </c>
       <c r="G155" s="13">
-        <v>4.4287999999999987E-2</v>
+        <v>5.5880000000000001E-3</v>
       </c>
       <c r="H155" s="13">
-        <v>2.7272727272727269E-8</v>
+        <v>1.1150097465886939E-7</v>
       </c>
       <c r="I155" s="13">
         <v>0</v>
@@ -8622,7 +8705,7 @@
         <v>1</v>
       </c>
       <c r="K155" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L155" s="15">
         <v>0</v>
@@ -8641,26 +8724,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="156" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="156" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A156" s="10"/>
       <c r="B156" s="11"/>
       <c r="C156" s="12" t="s">
-        <v>172</v>
+        <v>186</v>
       </c>
       <c r="D156" s="12" t="s">
-        <v>215</v>
+        <v>243</v>
       </c>
       <c r="E156" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F156" s="13">
-        <v>3.1175000000000001E-2</v>
+        <v>7.7619999999999998E-3</v>
       </c>
       <c r="G156" s="13">
-        <v>2.2269000000000001E-2</v>
+        <v>4.4879999999999998E-3</v>
       </c>
       <c r="H156" s="13">
-        <v>8.3333333333333335E-9</v>
+        <v>2.1163043478260869E-7</v>
       </c>
       <c r="I156" s="13">
         <v>0</v>
@@ -8669,7 +8752,7 @@
         <v>1</v>
       </c>
       <c r="K156" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L156" s="15">
         <v>0</v>
@@ -8688,26 +8771,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="157" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="157" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A157" s="10"/>
       <c r="B157" s="11"/>
       <c r="C157" s="12" t="s">
-        <v>160</v>
+        <v>81</v>
       </c>
       <c r="D157" s="12" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="E157" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F157" s="13">
-        <v>4.9117000000000001E-2</v>
+        <v>9.1520000000000004E-3</v>
       </c>
       <c r="G157" s="13">
-        <v>3.5083999999999997E-2</v>
+        <v>5.2919999999999998E-3</v>
       </c>
       <c r="H157" s="13">
-        <v>2.222222222222222E-8</v>
+        <v>9.9420625724217845E-8</v>
       </c>
       <c r="I157" s="13">
         <v>0</v>
@@ -8716,7 +8799,7 @@
         <v>1</v>
       </c>
       <c r="K157" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L157" s="15">
         <v>0</v>
@@ -8735,26 +8818,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="158" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="158" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A158" s="10"/>
       <c r="B158" s="11"/>
       <c r="C158" s="12" t="s">
-        <v>148</v>
+        <v>245</v>
       </c>
       <c r="D158" s="12" t="s">
-        <v>206</v>
+        <v>92</v>
       </c>
       <c r="E158" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F158" s="13">
-        <v>4.2698E-2</v>
+        <v>8.2290000000000002E-3</v>
       </c>
       <c r="G158" s="13">
-        <v>1.7025999999999999E-2</v>
+        <v>7.1540000000000006E-3</v>
       </c>
       <c r="H158" s="13">
-        <v>7.4999999999999993E-9</v>
+        <v>1.666981132075472E-7</v>
       </c>
       <c r="I158" s="13">
         <v>0</v>
@@ -8763,7 +8846,7 @@
         <v>1</v>
       </c>
       <c r="K158" s="14">
-        <v>6.1834213830208924</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L158" s="15">
         <v>0</v>
@@ -8782,26 +8865,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="159" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="159" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A159" s="10"/>
       <c r="B159" s="11"/>
       <c r="C159" s="12" t="s">
-        <v>231</v>
+        <v>84</v>
       </c>
       <c r="D159" s="12" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E159" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F159" s="13">
-        <v>1.4027E-2</v>
+        <v>1.5865000000000001E-2</v>
       </c>
       <c r="G159" s="13">
-        <v>1.0019E-2</v>
+        <v>6.4349999999999997E-3</v>
       </c>
       <c r="H159" s="13">
-        <v>6.6666666666666668E-9</v>
+        <v>1.552884615384615E-7</v>
       </c>
       <c r="I159" s="13">
         <v>0</v>
@@ -8810,7 +8893,7 @@
         <v>1</v>
       </c>
       <c r="K159" s="14">
-        <v>9.2751320745313386</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L159" s="15">
         <v>0</v>
@@ -8829,26 +8912,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="160" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="160" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A160" s="10"/>
       <c r="B160" s="11"/>
       <c r="C160" s="12" t="s">
-        <v>199</v>
+        <v>242</v>
       </c>
       <c r="D160" s="12" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="E160" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F160" s="13">
-        <v>1.4128E-2</v>
+        <v>9.389999999999999E-3</v>
       </c>
       <c r="G160" s="13">
-        <v>1.0092E-2</v>
+        <v>5.4300000000000008E-3</v>
       </c>
       <c r="H160" s="13">
-        <v>6.6666666666666668E-9</v>
+        <v>9.5593220338983041E-8</v>
       </c>
       <c r="I160" s="13">
         <v>0</v>
@@ -8857,7 +8940,7 @@
         <v>1</v>
       </c>
       <c r="K160" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L160" s="15">
         <v>0</v>
@@ -8876,26 +8959,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="161" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A161" s="10"/>
       <c r="B161" s="11"/>
       <c r="C161" s="12" t="s">
-        <v>131</v>
+        <v>247</v>
       </c>
       <c r="D161" s="12" t="s">
-        <v>213</v>
+        <v>172</v>
       </c>
       <c r="E161" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F161" s="13">
-        <v>1.9366999999999999E-2</v>
+        <v>6.3359999999999996E-3</v>
       </c>
       <c r="G161" s="13">
-        <v>1.3833E-2</v>
+        <v>2.5699999999999998E-3</v>
       </c>
       <c r="H161" s="13">
-        <v>1E-8</v>
+        <v>8.8780487804878061E-8</v>
       </c>
       <c r="I161" s="13">
         <v>0</v>
@@ -8904,7 +8987,7 @@
         <v>1</v>
       </c>
       <c r="K161" s="14">
-        <v>9.2751320745313386</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L161" s="15">
         <v>0</v>
@@ -8923,26 +9006,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="162" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A162" s="10"/>
       <c r="B162" s="11"/>
       <c r="C162" s="12" t="s">
-        <v>123</v>
+        <v>248</v>
       </c>
       <c r="D162" s="12" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="E162" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F162" s="13">
-        <v>3.2710999999999997E-2</v>
+        <v>4.9570999999999997E-2</v>
       </c>
       <c r="G162" s="13">
-        <v>2.8433E-2</v>
+        <v>3.5409000000000003E-2</v>
       </c>
       <c r="H162" s="13">
-        <v>4.2680921265067721E-7</v>
+        <v>8.8888888888888885E-9</v>
       </c>
       <c r="I162" s="13">
         <v>0</v>
@@ -8951,7 +9034,7 @@
         <v>1</v>
       </c>
       <c r="K162" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L162" s="15">
         <v>0</v>
@@ -8970,26 +9053,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="163" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="163" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A163" s="10"/>
       <c r="B163" s="11"/>
       <c r="C163" s="12" t="s">
-        <v>253</v>
+        <v>88</v>
       </c>
       <c r="D163" s="12" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="E163" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F163" s="13">
-        <v>9.389999999999999E-3</v>
+        <v>6.2004999999999998E-2</v>
       </c>
       <c r="G163" s="13">
-        <v>8.1620000000000009E-3</v>
+        <v>4.4287999999999987E-2</v>
       </c>
       <c r="H163" s="13">
-        <v>6.6457680250783701E-9</v>
+        <v>2.7272727272727269E-8</v>
       </c>
       <c r="I163" s="13">
         <v>0</v>
@@ -8998,7 +9081,7 @@
         <v>1</v>
       </c>
       <c r="K163" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L163" s="15">
         <v>0</v>
@@ -9017,26 +9100,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="164" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="164" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A164" s="10"/>
       <c r="B164" s="11"/>
       <c r="C164" s="12" t="s">
-        <v>253</v>
+        <v>169</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="E164" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F164" s="13">
-        <v>1.5790999999999999E-2</v>
+        <v>3.1175000000000001E-2</v>
       </c>
       <c r="G164" s="13">
-        <v>1.3726E-2</v>
+        <v>2.2269000000000001E-2</v>
       </c>
       <c r="H164" s="13">
-        <v>9.0132963988919676E-7</v>
+        <v>8.3333333333333335E-9</v>
       </c>
       <c r="I164" s="13">
         <v>0</v>
@@ -9045,7 +9128,7 @@
         <v>1</v>
       </c>
       <c r="K164" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L164" s="15">
         <v>0</v>
@@ -9064,26 +9147,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="165" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="165" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A165" s="10"/>
       <c r="B165" s="11"/>
       <c r="C165" s="12" t="s">
-        <v>101</v>
+        <v>157</v>
       </c>
       <c r="D165" s="12" t="s">
-        <v>119</v>
+        <v>248</v>
       </c>
       <c r="E165" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F165" s="13">
-        <v>1.4958000000000001E-2</v>
+        <v>4.9117000000000001E-2</v>
       </c>
       <c r="G165" s="13">
-        <v>8.6479999999999994E-3</v>
+        <v>3.5083999999999997E-2</v>
       </c>
       <c r="H165" s="13">
-        <v>2.9265536723163847E-7</v>
+        <v>2.222222222222222E-8</v>
       </c>
       <c r="I165" s="13">
         <v>0</v>
@@ -9092,7 +9175,7 @@
         <v>1</v>
       </c>
       <c r="K165" s="14">
-        <v>11.63938142686286</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L165" s="15">
         <v>0</v>
@@ -9111,26 +9194,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="166" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="166" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A166" s="10"/>
       <c r="B166" s="11"/>
       <c r="C166" s="12" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="D166" s="12" t="s">
-        <v>100</v>
+        <v>203</v>
       </c>
       <c r="E166" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F166" s="13">
-        <v>1.6424000000000001E-2</v>
+        <v>4.2698E-2</v>
       </c>
       <c r="G166" s="13">
-        <v>9.496000000000001E-3</v>
+        <v>1.7025999999999999E-2</v>
       </c>
       <c r="H166" s="13">
-        <v>1.186560693641618E-7</v>
+        <v>7.4999999999999993E-9</v>
       </c>
       <c r="I166" s="13">
         <v>0</v>
@@ -9139,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="K166" s="14">
-        <v>11.63938142686286</v>
+        <v>6.1834213830208924</v>
       </c>
       <c r="L166" s="15">
         <v>0</v>
@@ -9158,26 +9241,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="167" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="167" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A167" s="10"/>
       <c r="B167" s="11"/>
       <c r="C167" s="12" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="D167" s="12" t="s">
-        <v>253</v>
+        <v>227</v>
       </c>
       <c r="E167" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F167" s="13">
-        <v>1.0217E-2</v>
+        <v>1.4027E-2</v>
       </c>
       <c r="G167" s="13">
-        <v>8.881E-3</v>
+        <v>1.0019E-2</v>
       </c>
       <c r="H167" s="13">
-        <v>5.1553648068669529E-7</v>
+        <v>6.6666666666666668E-9</v>
       </c>
       <c r="I167" s="13">
         <v>0</v>
@@ -9186,7 +9269,7 @@
         <v>1</v>
       </c>
       <c r="K167" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L167" s="15">
         <v>0</v>
@@ -9205,26 +9288,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="168" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="168" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A168" s="10"/>
       <c r="B168" s="11"/>
       <c r="C168" s="12" t="s">
-        <v>130</v>
+        <v>196</v>
       </c>
       <c r="D168" s="12" t="s">
-        <v>255</v>
+        <v>155</v>
       </c>
       <c r="E168" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F168" s="13">
-        <v>7.1139999999999997E-3</v>
+        <v>1.4128E-2</v>
       </c>
       <c r="G168" s="13">
-        <v>6.1860000000000014E-3</v>
+        <v>1.0092E-2</v>
       </c>
       <c r="H168" s="13">
-        <v>9.1743119266055035E-9</v>
+        <v>6.6666666666666668E-9</v>
       </c>
       <c r="I168" s="13">
         <v>0</v>
@@ -9233,7 +9316,7 @@
         <v>1</v>
       </c>
       <c r="K168" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L168" s="15">
         <v>0</v>
@@ -9252,26 +9335,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="169" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="169" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A169" s="10"/>
       <c r="B169" s="11"/>
       <c r="C169" s="12" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>110</v>
+        <v>210</v>
       </c>
       <c r="E169" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F169" s="13">
-        <v>1.2296E-2</v>
+        <v>1.9366999999999999E-2</v>
       </c>
       <c r="G169" s="13">
-        <v>1.0688E-2</v>
+        <v>1.3833E-2</v>
       </c>
       <c r="H169" s="13">
-        <v>7.0099644128113876E-7</v>
+        <v>1E-8</v>
       </c>
       <c r="I169" s="13">
         <v>0</v>
@@ -9280,7 +9363,7 @@
         <v>1</v>
       </c>
       <c r="K169" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L169" s="15">
         <v>0</v>
@@ -9299,26 +9382,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="170" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="170" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A170" s="10"/>
       <c r="B170" s="11"/>
       <c r="C170" s="12" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="D170" s="12" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="E170" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F170" s="13">
-        <v>1.4585000000000001E-2</v>
+        <v>3.2710999999999997E-2</v>
       </c>
       <c r="G170" s="13">
-        <v>8.4329999999999995E-3</v>
+        <v>2.8433E-2</v>
       </c>
       <c r="H170" s="13">
-        <v>1.226431718061674E-7</v>
+        <v>4.2680921265067721E-7</v>
       </c>
       <c r="I170" s="13">
         <v>0</v>
@@ -9327,7 +9410,7 @@
         <v>1</v>
       </c>
       <c r="K170" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L170" s="15">
         <v>0</v>
@@ -9346,26 +9429,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="171" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="171" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A171" s="10"/>
       <c r="B171" s="11"/>
       <c r="C171" s="12" t="s">
-        <v>163</v>
+        <v>249</v>
       </c>
       <c r="D171" s="12" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E171" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F171" s="13">
-        <v>1.145E-2</v>
+        <v>9.389999999999999E-3</v>
       </c>
       <c r="G171" s="13">
-        <v>6.62E-3</v>
+        <v>8.1620000000000009E-3</v>
       </c>
       <c r="H171" s="13">
-        <v>9.6762503020053146E-9</v>
+        <v>6.6457680250783701E-9</v>
       </c>
       <c r="I171" s="13">
         <v>0</v>
@@ -9374,7 +9457,7 @@
         <v>1</v>
       </c>
       <c r="K171" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L171" s="15">
         <v>0</v>
@@ -9393,26 +9476,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="172" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="172" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A172" s="10"/>
       <c r="B172" s="11"/>
       <c r="C172" s="12" t="s">
-        <v>118</v>
+        <v>249</v>
       </c>
       <c r="D172" s="12" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="E172" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F172" s="13">
-        <v>9.2840000000000006E-3</v>
+        <v>1.5790999999999999E-2</v>
       </c>
       <c r="G172" s="13">
-        <v>5.3680000000000004E-3</v>
+        <v>1.3726E-2</v>
       </c>
       <c r="H172" s="13">
-        <v>2.1743119266055051E-7</v>
+        <v>9.0132963988919676E-7</v>
       </c>
       <c r="I172" s="13">
         <v>0</v>
@@ -9421,7 +9504,7 @@
         <v>1</v>
       </c>
       <c r="K172" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L172" s="15">
         <v>0</v>
@@ -9440,26 +9523,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="173" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="173" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A173" s="10"/>
       <c r="B173" s="11"/>
       <c r="C173" s="12" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="D173" s="12" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="E173" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F173" s="13">
-        <v>1.2194E-2</v>
+        <v>1.4958000000000001E-2</v>
       </c>
       <c r="G173" s="13">
-        <v>7.0500000000000007E-3</v>
+        <v>8.6479999999999994E-3</v>
       </c>
       <c r="H173" s="13">
-        <v>3.5750000000000002E-7</v>
+        <v>2.9265536723163847E-7</v>
       </c>
       <c r="I173" s="13">
         <v>0</v>
@@ -9487,26 +9570,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="174" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="174" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A174" s="10"/>
       <c r="B174" s="11"/>
       <c r="C174" s="12" t="s">
-        <v>258</v>
+        <v>96</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>259</v>
+        <v>97</v>
       </c>
       <c r="E174" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F174" s="13">
-        <v>1.0024E-2</v>
+        <v>1.6424000000000001E-2</v>
       </c>
       <c r="G174" s="13">
-        <v>4.0659999999999993E-3</v>
+        <v>9.496000000000001E-3</v>
       </c>
       <c r="H174" s="13">
-        <v>9.8484848484848481E-9</v>
+        <v>1.186560693641618E-7</v>
       </c>
       <c r="I174" s="13">
         <v>0</v>
@@ -9515,7 +9598,7 @@
         <v>1</v>
       </c>
       <c r="K174" s="14">
-        <v>9.1296398066955522</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L174" s="15">
         <v>0</v>
@@ -9534,26 +9617,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="175" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="175" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A175" s="10"/>
       <c r="B175" s="11"/>
       <c r="C175" s="12" t="s">
-        <v>130</v>
+        <v>239</v>
       </c>
       <c r="D175" s="12" t="s">
-        <v>98</v>
+        <v>249</v>
       </c>
       <c r="E175" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F175" s="13">
-        <v>5.653E-3</v>
+        <v>1.0217E-2</v>
       </c>
       <c r="G175" s="13">
-        <v>4.9130000000000007E-3</v>
+        <v>8.881E-3</v>
       </c>
       <c r="H175" s="13">
-        <v>7.3496659242761688E-8</v>
+        <v>5.1553648068669529E-7</v>
       </c>
       <c r="I175" s="13">
         <v>0</v>
@@ -9581,26 +9664,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="176" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A176" s="10"/>
       <c r="B176" s="11"/>
       <c r="C176" s="12" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>157</v>
+        <v>251</v>
       </c>
       <c r="E176" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F176" s="13">
-        <v>6.1410000000000006E-3</v>
+        <v>7.1139999999999997E-3</v>
       </c>
       <c r="G176" s="13">
-        <v>5.339E-3</v>
+        <v>6.1860000000000014E-3</v>
       </c>
       <c r="H176" s="13">
-        <v>3.4935714285714288E-7</v>
+        <v>9.1743119266055035E-9</v>
       </c>
       <c r="I176" s="13">
         <v>0</v>
@@ -9628,26 +9711,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="177" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="177" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A177" s="10"/>
       <c r="B177" s="11"/>
       <c r="C177" s="12" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="D177" s="12" t="s">
-        <v>258</v>
+        <v>107</v>
       </c>
       <c r="E177" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F177" s="13">
-        <v>1.4540000000000001E-2</v>
+        <v>1.2296E-2</v>
       </c>
       <c r="G177" s="13">
-        <v>5.8979999999999996E-3</v>
+        <v>1.0688E-2</v>
       </c>
       <c r="H177" s="13">
-        <v>9.5873573309920966E-9</v>
+        <v>7.0099644128113876E-7</v>
       </c>
       <c r="I177" s="13">
         <v>0</v>
@@ -9656,7 +9739,7 @@
         <v>1</v>
       </c>
       <c r="K177" s="14">
-        <v>9.1296398066955522</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L177" s="15">
         <v>0</v>
@@ -9675,26 +9758,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="178" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="178" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A178" s="10"/>
       <c r="B178" s="11"/>
       <c r="C178" s="12" t="s">
-        <v>184</v>
+        <v>110</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>161</v>
+        <v>252</v>
       </c>
       <c r="E178" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F178" s="13">
-        <v>1.3528E-2</v>
+        <v>1.4585000000000001E-2</v>
       </c>
       <c r="G178" s="13">
-        <v>7.8219999999999991E-3</v>
+        <v>8.4329999999999995E-3</v>
       </c>
       <c r="H178" s="13">
-        <v>7.9544758152768663E-8</v>
+        <v>1.226431718061674E-7</v>
       </c>
       <c r="I178" s="13">
         <v>0</v>
@@ -9722,26 +9805,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="179" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="179" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A179" s="10"/>
       <c r="B179" s="11"/>
       <c r="C179" s="12" t="s">
-        <v>239</v>
+        <v>160</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>108</v>
+        <v>253</v>
       </c>
       <c r="E179" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F179" s="13">
-        <v>7.1329999999999996E-3</v>
+        <v>1.145E-2</v>
       </c>
       <c r="G179" s="13">
-        <v>6.1989999999999996E-3</v>
+        <v>6.62E-3</v>
       </c>
       <c r="H179" s="13">
-        <v>1.726141078838174E-7</v>
+        <v>9.6762503020053146E-9</v>
       </c>
       <c r="I179" s="13">
         <v>0</v>
@@ -9750,7 +9833,7 @@
         <v>1</v>
       </c>
       <c r="K179" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L179" s="15">
         <v>0</v>
@@ -9769,26 +9852,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="180" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="180" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A180" s="10"/>
       <c r="B180" s="11"/>
       <c r="C180" s="12" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>203</v>
+        <v>150</v>
       </c>
       <c r="E180" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F180" s="13">
-        <v>3.5699999999999998E-3</v>
+        <v>9.2840000000000006E-3</v>
       </c>
       <c r="G180" s="13">
-        <v>3.1029999999999999E-3</v>
+        <v>5.3680000000000004E-3</v>
       </c>
       <c r="H180" s="13">
-        <v>1.8617283950617279E-7</v>
+        <v>2.1743119266055051E-7</v>
       </c>
       <c r="I180" s="13">
         <v>0</v>
@@ -9797,7 +9880,7 @@
         <v>1</v>
       </c>
       <c r="K180" s="14">
-        <v>15.240315055798551</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L180" s="15">
         <v>0</v>
@@ -9816,26 +9899,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="181" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="181" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A181" s="10"/>
       <c r="B181" s="11"/>
       <c r="C181" s="12" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="D181" s="12" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="E181" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F181" s="13">
-        <v>1.0217E-2</v>
+        <v>1.2194E-2</v>
       </c>
       <c r="G181" s="13">
-        <v>5.9069999999999999E-3</v>
+        <v>7.0500000000000007E-3</v>
       </c>
       <c r="H181" s="13">
-        <v>1.2353591160221001E-7</v>
+        <v>3.5750000000000002E-7</v>
       </c>
       <c r="I181" s="13">
         <v>0</v>
@@ -9863,26 +9946,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="182" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="182" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A182" s="10"/>
       <c r="B182" s="11"/>
       <c r="C182" s="12" t="s">
-        <v>116</v>
+        <v>254</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>90</v>
+        <v>255</v>
       </c>
       <c r="E182" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F182" s="13">
-        <v>1.3242E-2</v>
+        <v>1.0024E-2</v>
       </c>
       <c r="G182" s="13">
-        <v>5.3710000000000008E-3</v>
+        <v>4.0659999999999993E-3</v>
       </c>
       <c r="H182" s="13">
-        <v>1.8201284796573871E-8</v>
+        <v>9.8484848484848481E-9</v>
       </c>
       <c r="I182" s="13">
         <v>0</v>
@@ -9910,26 +9993,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="183" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="183" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A183" s="10"/>
       <c r="B183" s="11"/>
       <c r="C183" s="12" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="D183" s="12" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E183" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F183" s="13">
-        <v>4.0735999999999987E-2</v>
+        <v>5.653E-3</v>
       </c>
       <c r="G183" s="13">
-        <v>3.5409999999999997E-2</v>
+        <v>4.9130000000000007E-3</v>
       </c>
       <c r="H183" s="13">
-        <v>3.4689265645707981E-9</v>
+        <v>7.3496659242761688E-8</v>
       </c>
       <c r="I183" s="13">
         <v>0</v>
@@ -9938,7 +10021,7 @@
         <v>1</v>
       </c>
       <c r="K183" s="14">
-        <v>15.16756892188066</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L183" s="15">
         <v>0</v>
@@ -9957,26 +10040,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="184" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="184" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A184" s="10"/>
       <c r="B184" s="11"/>
       <c r="C184" s="12" t="s">
-        <v>128</v>
+        <v>173</v>
       </c>
       <c r="D184" s="12" t="s">
-        <v>261</v>
+        <v>154</v>
       </c>
       <c r="E184" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F184" s="13">
-        <v>1.0992999999999999E-2</v>
+        <v>6.1410000000000006E-3</v>
       </c>
       <c r="G184" s="13">
-        <v>6.3569999999999998E-3</v>
+        <v>5.339E-3</v>
       </c>
       <c r="H184" s="13">
-        <v>6.6220735785953189E-8</v>
+        <v>3.4935714285714288E-7</v>
       </c>
       <c r="I184" s="13">
         <v>0</v>
@@ -9985,7 +10068,7 @@
         <v>1</v>
       </c>
       <c r="K184" s="14">
-        <v>11.63938142686286</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L184" s="15">
         <v>0</v>
@@ -10004,26 +10087,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="185" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="185" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A185" s="10"/>
       <c r="B185" s="11"/>
       <c r="C185" s="12" t="s">
-        <v>234</v>
+        <v>151</v>
       </c>
       <c r="D185" s="12" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="E185" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F185" s="13">
-        <v>3.7913000000000002E-2</v>
+        <v>1.4540000000000001E-2</v>
       </c>
       <c r="G185" s="13">
-        <v>2.7081000000000001E-2</v>
+        <v>5.8979999999999996E-3</v>
       </c>
       <c r="H185" s="13">
-        <v>8.7500000000000006E-9</v>
+        <v>9.5873573309920966E-9</v>
       </c>
       <c r="I185" s="13">
         <v>0</v>
@@ -10032,7 +10115,7 @@
         <v>1</v>
       </c>
       <c r="K185" s="14">
-        <v>9.2751320745313386</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L185" s="15">
         <v>0</v>
@@ -10051,26 +10134,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="186" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="186" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A186" s="10"/>
       <c r="B186" s="11"/>
       <c r="C186" s="12" t="s">
-        <v>91</v>
+        <v>181</v>
       </c>
       <c r="D186" s="12" t="s">
-        <v>231</v>
+        <v>158</v>
       </c>
       <c r="E186" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F186" s="13">
-        <v>1.9536000000000001E-2</v>
+        <v>1.3528E-2</v>
       </c>
       <c r="G186" s="13">
-        <v>1.3953999999999999E-2</v>
+        <v>7.8219999999999991E-3</v>
       </c>
       <c r="H186" s="13">
-        <v>7.4999999999999993E-9</v>
+        <v>7.9544758152768663E-8</v>
       </c>
       <c r="I186" s="13">
         <v>0</v>
@@ -10079,7 +10162,7 @@
         <v>1</v>
       </c>
       <c r="K186" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L186" s="15">
         <v>0</v>
@@ -10098,26 +10181,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="187" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="187" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A187" s="10"/>
       <c r="B187" s="11"/>
       <c r="C187" s="12" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="D187" s="12" t="s">
-        <v>177</v>
+        <v>105</v>
       </c>
       <c r="E187" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F187" s="13">
-        <v>1.3502999999999999E-2</v>
+        <v>7.1329999999999996E-3</v>
       </c>
       <c r="G187" s="13">
-        <v>9.6460000000000001E-3</v>
+        <v>6.1989999999999996E-3</v>
       </c>
       <c r="H187" s="13">
-        <v>6.6666666666666668E-9</v>
+        <v>1.726141078838174E-7</v>
       </c>
       <c r="I187" s="13">
         <v>0</v>
@@ -10126,7 +10209,7 @@
         <v>1</v>
       </c>
       <c r="K187" s="14">
-        <v>9.2751320745313386</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L187" s="15">
         <v>0</v>
@@ -10145,26 +10228,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="188" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="188" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A188" s="10"/>
       <c r="B188" s="11"/>
       <c r="C188" s="12" t="s">
-        <v>221</v>
+        <v>94</v>
       </c>
       <c r="D188" s="12" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="E188" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F188" s="13">
-        <v>1.4075000000000001E-2</v>
+        <v>3.5699999999999998E-3</v>
       </c>
       <c r="G188" s="13">
-        <v>1.0054E-2</v>
+        <v>3.1029999999999999E-3</v>
       </c>
       <c r="H188" s="13">
-        <v>6.6666666666666668E-9</v>
+        <v>1.8617283950617279E-7</v>
       </c>
       <c r="I188" s="13">
         <v>0</v>
@@ -10173,7 +10256,7 @@
         <v>1</v>
       </c>
       <c r="K188" s="14">
-        <v>9.2751320745313386</v>
+        <v>15.240315055798551</v>
       </c>
       <c r="L188" s="15">
         <v>0</v>
@@ -10192,26 +10275,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="189" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="189" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A189" s="10"/>
       <c r="B189" s="11"/>
       <c r="C189" s="12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="D189" s="12" t="s">
-        <v>178</v>
+        <v>256</v>
       </c>
       <c r="E189" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F189" s="13">
-        <v>6.4770000000000001E-3</v>
+        <v>1.0217E-2</v>
       </c>
       <c r="G189" s="13">
-        <v>4.6259999999999999E-3</v>
+        <v>5.9069999999999999E-3</v>
       </c>
       <c r="H189" s="13">
-        <v>5.0000000000000001E-9</v>
+        <v>1.2353591160221001E-7</v>
       </c>
       <c r="I189" s="13">
         <v>0</v>
@@ -10220,7 +10303,7 @@
         <v>1</v>
       </c>
       <c r="K189" s="14">
-        <v>9.2751320745313386</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L189" s="15">
         <v>0</v>
@@ -10239,26 +10322,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="190" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="190" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A190" s="10"/>
       <c r="B190" s="11"/>
       <c r="C190" s="12" t="s">
-        <v>214</v>
+        <v>113</v>
       </c>
       <c r="D190" s="12" t="s">
-        <v>223</v>
+        <v>87</v>
       </c>
       <c r="E190" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F190" s="13">
-        <v>3.052E-3</v>
+        <v>1.3242E-2</v>
       </c>
       <c r="G190" s="13">
-        <v>2.1800000000000001E-3</v>
+        <v>5.3710000000000008E-3</v>
       </c>
       <c r="H190" s="13">
-        <v>5.0000000000000001E-9</v>
+        <v>1.8201284796573871E-8</v>
       </c>
       <c r="I190" s="13">
         <v>0</v>
@@ -10267,7 +10350,7 @@
         <v>1</v>
       </c>
       <c r="K190" s="14">
-        <v>9.8207280789155327</v>
+        <v>9.1296398066955522</v>
       </c>
       <c r="L190" s="15">
         <v>0</v>
@@ -10286,26 +10369,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="191" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="191" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A191" s="10"/>
       <c r="B191" s="11"/>
       <c r="C191" s="12" t="s">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="D191" s="12" t="s">
-        <v>188</v>
+        <v>88</v>
       </c>
       <c r="E191" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F191" s="13">
-        <v>5.4299999999999997E-4</v>
+        <v>4.0735999999999987E-2</v>
       </c>
       <c r="G191" s="13">
-        <v>4.7199999999999998E-4</v>
+        <v>3.5409999999999997E-2</v>
       </c>
       <c r="H191" s="13">
-        <v>1.1999999999999999E-7</v>
+        <v>3.4689265645707981E-9</v>
       </c>
       <c r="I191" s="13">
         <v>0</v>
@@ -10314,7 +10397,7 @@
         <v>1</v>
       </c>
       <c r="K191" s="14">
-        <v>15.240315055798551</v>
+        <v>15.16756892188066</v>
       </c>
       <c r="L191" s="15">
         <v>0</v>
@@ -10333,26 +10416,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="192" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="192" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A192" s="10"/>
       <c r="B192" s="11"/>
       <c r="C192" s="12" t="s">
-        <v>258</v>
+        <v>125</v>
       </c>
       <c r="D192" s="12" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E192" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F192" s="13">
-        <v>8.5929999999999999E-3</v>
+        <v>1.0992999999999999E-2</v>
       </c>
       <c r="G192" s="13">
-        <v>3.4840000000000001E-3</v>
+        <v>6.3569999999999998E-3</v>
       </c>
       <c r="H192" s="13">
-        <v>9.3128834355828231E-9</v>
+        <v>6.6220735785953189E-8</v>
       </c>
       <c r="I192" s="13">
         <v>0</v>
@@ -10361,7 +10444,7 @@
         <v>1</v>
       </c>
       <c r="K192" s="14">
-        <v>9.1296398066955522</v>
+        <v>11.63938142686286</v>
       </c>
       <c r="L192" s="15">
         <v>0</v>
@@ -10380,26 +10463,26 @@
         <v>80</v>
       </c>
     </row>
-    <row r="193" spans="1:19" x14ac:dyDescent="0.5">
+    <row r="193" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A193" s="10"/>
       <c r="B193" s="11"/>
       <c r="C193" s="12" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="D193" s="12" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="E193" s="12" t="s">
         <v>76</v>
       </c>
       <c r="F193" s="13">
-        <v>7.7149999999999996E-3</v>
+        <v>3.7913000000000002E-2</v>
       </c>
       <c r="G193" s="13">
-        <v>6.7060000000000002E-3</v>
+        <v>2.7081000000000001E-2</v>
       </c>
       <c r="H193" s="13">
-        <v>3.3494318181818169E-7</v>
+        <v>8.7500000000000006E-9</v>
       </c>
       <c r="I193" s="13">
         <v>0</v>
@@ -10408,7 +10491,7 @@
         <v>1</v>
       </c>
       <c r="K193" s="14">
-        <v>15.240315055798551</v>
+        <v>9.2751320745313386</v>
       </c>
       <c r="L193" s="15">
         <v>0</v>
@@ -10424,6 +10507,382 @@
         <v>79</v>
       </c>
       <c r="S193" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="194" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A194" s="10"/>
+      <c r="B194" s="11"/>
+      <c r="C194" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D194" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="E194" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F194" s="13">
+        <v>1.9536000000000001E-2</v>
+      </c>
+      <c r="G194" s="13">
+        <v>1.3953999999999999E-2</v>
+      </c>
+      <c r="H194" s="13">
+        <v>7.4999999999999993E-9</v>
+      </c>
+      <c r="I194" s="13">
+        <v>0</v>
+      </c>
+      <c r="J194" s="13">
+        <v>1</v>
+      </c>
+      <c r="K194" s="14">
+        <v>9.2751320745313386</v>
+      </c>
+      <c r="L194" s="15">
+        <v>0</v>
+      </c>
+      <c r="M194" s="16"/>
+      <c r="N194" s="16"/>
+      <c r="O194" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P194" s="15"/>
+      <c r="Q194" s="15"/>
+      <c r="R194" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S194" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="195" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A195" s="10"/>
+      <c r="B195" s="11"/>
+      <c r="C195" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D195" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E195" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F195" s="13">
+        <v>1.3502999999999999E-2</v>
+      </c>
+      <c r="G195" s="13">
+        <v>9.6460000000000001E-3</v>
+      </c>
+      <c r="H195" s="13">
+        <v>6.6666666666666668E-9</v>
+      </c>
+      <c r="I195" s="13">
+        <v>0</v>
+      </c>
+      <c r="J195" s="13">
+        <v>1</v>
+      </c>
+      <c r="K195" s="14">
+        <v>9.2751320745313386</v>
+      </c>
+      <c r="L195" s="15">
+        <v>0</v>
+      </c>
+      <c r="M195" s="16"/>
+      <c r="N195" s="16"/>
+      <c r="O195" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P195" s="15"/>
+      <c r="Q195" s="15"/>
+      <c r="R195" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S195" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="196" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A196" s="10"/>
+      <c r="B196" s="11"/>
+      <c r="C196" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="D196" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="E196" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F196" s="13">
+        <v>1.4075000000000001E-2</v>
+      </c>
+      <c r="G196" s="13">
+        <v>1.0054E-2</v>
+      </c>
+      <c r="H196" s="13">
+        <v>6.6666666666666668E-9</v>
+      </c>
+      <c r="I196" s="13">
+        <v>0</v>
+      </c>
+      <c r="J196" s="13">
+        <v>1</v>
+      </c>
+      <c r="K196" s="14">
+        <v>9.2751320745313386</v>
+      </c>
+      <c r="L196" s="15">
+        <v>0</v>
+      </c>
+      <c r="M196" s="16"/>
+      <c r="N196" s="16"/>
+      <c r="O196" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P196" s="15"/>
+      <c r="Q196" s="15"/>
+      <c r="R196" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S196" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="197" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A197" s="10"/>
+      <c r="B197" s="11"/>
+      <c r="C197" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="D197" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E197" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F197" s="13">
+        <v>6.4770000000000001E-3</v>
+      </c>
+      <c r="G197" s="13">
+        <v>4.6259999999999999E-3</v>
+      </c>
+      <c r="H197" s="13">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="I197" s="13">
+        <v>0</v>
+      </c>
+      <c r="J197" s="13">
+        <v>1</v>
+      </c>
+      <c r="K197" s="14">
+        <v>9.2751320745313386</v>
+      </c>
+      <c r="L197" s="15">
+        <v>0</v>
+      </c>
+      <c r="M197" s="16"/>
+      <c r="N197" s="16"/>
+      <c r="O197" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P197" s="15"/>
+      <c r="Q197" s="15"/>
+      <c r="R197" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S197" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="198" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A198" s="10"/>
+      <c r="B198" s="11"/>
+      <c r="C198" s="12" t="s">
+        <v>211</v>
+      </c>
+      <c r="D198" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="E198" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F198" s="13">
+        <v>3.052E-3</v>
+      </c>
+      <c r="G198" s="13">
+        <v>2.1800000000000001E-3</v>
+      </c>
+      <c r="H198" s="13">
+        <v>5.0000000000000001E-9</v>
+      </c>
+      <c r="I198" s="13">
+        <v>0</v>
+      </c>
+      <c r="J198" s="13">
+        <v>1</v>
+      </c>
+      <c r="K198" s="14">
+        <v>9.8207280789155327</v>
+      </c>
+      <c r="L198" s="15">
+        <v>0</v>
+      </c>
+      <c r="M198" s="16"/>
+      <c r="N198" s="16"/>
+      <c r="O198" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P198" s="15"/>
+      <c r="Q198" s="15"/>
+      <c r="R198" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S198" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="199" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A199" s="10"/>
+      <c r="B199" s="11"/>
+      <c r="C199" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D199" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="E199" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F199" s="13">
+        <v>5.4299999999999997E-4</v>
+      </c>
+      <c r="G199" s="13">
+        <v>4.7199999999999998E-4</v>
+      </c>
+      <c r="H199" s="13">
+        <v>1.1999999999999999E-7</v>
+      </c>
+      <c r="I199" s="13">
+        <v>0</v>
+      </c>
+      <c r="J199" s="13">
+        <v>1</v>
+      </c>
+      <c r="K199" s="14">
+        <v>15.240315055798551</v>
+      </c>
+      <c r="L199" s="15">
+        <v>0</v>
+      </c>
+      <c r="M199" s="16"/>
+      <c r="N199" s="16"/>
+      <c r="O199" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P199" s="15"/>
+      <c r="Q199" s="15"/>
+      <c r="R199" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S199" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="200" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A200" s="10"/>
+      <c r="B200" s="11"/>
+      <c r="C200" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="D200" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="E200" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F200" s="13">
+        <v>8.5929999999999999E-3</v>
+      </c>
+      <c r="G200" s="13">
+        <v>3.4840000000000001E-3</v>
+      </c>
+      <c r="H200" s="13">
+        <v>9.3128834355828231E-9</v>
+      </c>
+      <c r="I200" s="13">
+        <v>0</v>
+      </c>
+      <c r="J200" s="13">
+        <v>1</v>
+      </c>
+      <c r="K200" s="14">
+        <v>9.1296398066955522</v>
+      </c>
+      <c r="L200" s="15">
+        <v>0</v>
+      </c>
+      <c r="M200" s="16"/>
+      <c r="N200" s="16"/>
+      <c r="O200" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P200" s="15"/>
+      <c r="Q200" s="15"/>
+      <c r="R200" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S200" s="17" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="201" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A201" s="10"/>
+      <c r="B201" s="11"/>
+      <c r="C201" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="D201" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="E201" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="F201" s="13">
+        <v>7.7149999999999996E-3</v>
+      </c>
+      <c r="G201" s="13">
+        <v>6.7060000000000002E-3</v>
+      </c>
+      <c r="H201" s="13">
+        <v>3.3494318181818169E-7</v>
+      </c>
+      <c r="I201" s="13">
+        <v>0</v>
+      </c>
+      <c r="J201" s="13">
+        <v>1</v>
+      </c>
+      <c r="K201" s="14">
+        <v>15.240315055798551</v>
+      </c>
+      <c r="L201" s="15">
+        <v>0</v>
+      </c>
+      <c r="M201" s="16"/>
+      <c r="N201" s="16"/>
+      <c r="O201" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="P201" s="15"/>
+      <c r="Q201" s="15"/>
+      <c r="R201" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="S201" s="17" t="s">
         <v>80</v>
       </c>
     </row>
